--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -11,6 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name=" Registry" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="MOSAIC_Countries">Reference!$A$2:$A$15</definedName>
+    <definedName name="MOSAIC_Themes">Reference!$C$2:$C$14</definedName>
+    <definedName name="MOSAIC_LLs">Reference!$K$2:$K$14</definedName>
+    <definedName name="MOSAIC_DataTypes">Reference!$E$2:$E$6</definedName>
+    <definedName name="MOSAIC_Sources">Reference!$G$2:$G$17</definedName>
+    <definedName name="MOSAIC_Access">Reference!$I$2:$I$4</definedName>
+    <definedName name="MOSAIC_Migration">Reference!$O$2:$O$3</definedName>
+    <definedName name="MOSAIC_UpdFreq">Reference!$Q$2:$Q$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$105</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">' Registry'!$1:$2</definedName>
   </definedNames>
@@ -2382,7 +2390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W105"/>
+  <dimension ref="A1:AD200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.5" defaultRowHeight="14"/>
   <cols>
     <col width="24" customWidth="1" style="8" min="1" max="1"/>
@@ -2681,8 +2689,10 @@
           <t>Admin - MFLLs Boundary</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
-        <v>2025</v>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
@@ -2723,8 +2733,10 @@
         </is>
       </c>
       <c r="S3" s="5" t="n"/>
-      <c r="T3" s="4" t="n">
-        <v>2026</v>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U3" s="11" t="inlineStr">
         <is>
@@ -2813,8 +2825,8 @@
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Related data set: Sentinel 2. Landsat 7, Landsat 8
-Method: Hierarchical classification approach. </t>
+          <t>Related data set: Sentinel 2. Landsat 7, Landsat 8
+Method: Hierarchical classification approach.</t>
         </is>
       </c>
       <c r="S4" s="5" t="n"/>
@@ -2866,8 +2878,10 @@
           <t>Raster</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>5000</v>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -2960,8 +2974,10 @@
           <t>Tabular</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>25000</v>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -3007,15 +3023,17 @@
         </is>
       </c>
       <c r="S6" s="5" t="n"/>
-      <c r="T6" s="4" t="n">
-        <v>2025</v>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="U6" s="11" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="V6" s="12" t="inlineStr">
+      <c r="V6" s="21" t="inlineStr">
         <is>
           <t>https://imdpune.gov.in/cmpg/Griddata/Rainfall_25_NetCDF.html</t>
         </is>
@@ -3057,8 +3075,10 @@
           <t>Village level</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
-        <v>2023</v>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
@@ -3099,8 +3119,10 @@
         </is>
       </c>
       <c r="S7" s="5" t="n"/>
-      <c r="T7" s="4" t="n">
-        <v>2023</v>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="U7" s="11" t="inlineStr">
         <is>
@@ -3149,8 +3171,10 @@
           <t>Village level</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>2023</v>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -3191,15 +3215,17 @@
         </is>
       </c>
       <c r="S8" s="5" t="n"/>
-      <c r="T8" s="4" t="n">
-        <v>2023</v>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="U8" s="11" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="V8" s="10" t="inlineStr">
+      <c r="V8" s="21" t="inlineStr">
         <is>
           <t>https://missionantyodaya.dord.gov.in/</t>
         </is>
@@ -3285,15 +3311,17 @@
         </is>
       </c>
       <c r="S9" s="5" t="n"/>
-      <c r="T9" s="4" t="n">
-        <v>2019</v>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
       </c>
       <c r="U9" s="11" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="V9" s="12" t="inlineStr">
+      <c r="V9" s="10" t="inlineStr">
         <is>
           <t>Internal (Available on request)
 https://indiawpatlas.shinyapps.io/wpatlas/#/trends</t>
@@ -3336,8 +3364,10 @@
           <t>District level</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>2025</v>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -3378,15 +3408,17 @@
         </is>
       </c>
       <c r="S10" s="5" t="n"/>
-      <c r="T10" s="4" t="n">
-        <v>2025</v>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="U10" s="11" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="V10" s="12" t="inlineStr">
+      <c r="V10" s="21" t="inlineStr">
         <is>
           <t>Internal (Available on request)
 https://solaready.iwmi.org/india/</t>
@@ -3429,8 +3461,10 @@
           <t>District level</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>2023</v>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -3471,15 +3505,17 @@
         </is>
       </c>
       <c r="S11" s="5" t="n"/>
-      <c r="T11" s="4" t="n">
-        <v>2024</v>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="U11" s="11" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="V11" s="22" t="inlineStr">
+      <c r="V11" s="10" t="inlineStr">
         <is>
           <t>https://www.data.gov.in/catalog/average-yield-principal-crops</t>
         </is>
@@ -3565,15 +3601,17 @@
         </is>
       </c>
       <c r="S12" s="5" t="n"/>
-      <c r="T12" s="4" t="n">
-        <v>2019</v>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
       </c>
       <c r="U12" s="11" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="V12" s="13" t="inlineStr">
+      <c r="V12" s="21" t="inlineStr">
         <is>
           <t>https://www.data.gov.in/resource/district-wise-details-livestock-population-madhya-pradesh-20th-livestock-census-2019</t>
         </is>
@@ -3659,15 +3697,17 @@
         </is>
       </c>
       <c r="S13" s="5" t="n"/>
-      <c r="T13" s="4" t="n">
-        <v>2024</v>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="U13" s="11" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="V13" s="12" t="inlineStr">
+      <c r="V13" s="10" t="inlineStr">
         <is>
           <t>https://soilhealth.dac.gov.in/legacy-maps/Cycle_II/MADHYA%20PRADESH/23/MANDLA/415</t>
         </is>
@@ -3753,15 +3793,17 @@
         </is>
       </c>
       <c r="S14" s="5" t="n"/>
-      <c r="T14" s="4" t="n">
-        <v>2025</v>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="U14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seasonal </t>
-        </is>
-      </c>
-      <c r="V14" s="10" t="inlineStr">
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="V14" s="21" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
         </is>
@@ -3803,8 +3845,10 @@
           <t>250 m</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>2024</v>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -3845,15 +3889,17 @@
         </is>
       </c>
       <c r="S15" s="5" t="n"/>
-      <c r="T15" s="4" t="n">
-        <v>2024</v>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="U15" s="11" t="inlineStr">
         <is>
           <t>Static</t>
         </is>
       </c>
-      <c r="V15" s="21" t="inlineStr">
+      <c r="V15" s="10" t="inlineStr">
         <is>
           <t>https://zenodo.org/records/10846594
 https://zenodo.org/records/6505510
@@ -3909,9 +3955,8 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core Stack (Open access)
-Sudharsan Malaiappan - s.maliappan@cgiar.org
-</t>
+          <t>Core Stack (Open access)
+Sudharsan Malaiappan - s.maliappan@cgiar.org</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
@@ -3943,8 +3988,10 @@
         </is>
       </c>
       <c r="S16" s="5" t="n"/>
-      <c r="T16" s="4" t="n">
-        <v>2024</v>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="U16" s="11" t="inlineStr">
         <is>
@@ -4006,9 +4053,8 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core Stack (Open access)
-Sudharsan Malaiappan - s.maliappan@cgiar.org
-</t>
+          <t>Core Stack (Open access)
+Sudharsan Malaiappan - s.maliappan@cgiar.org</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -4040,15 +4086,17 @@
         </is>
       </c>
       <c r="S17" s="5" t="n"/>
-      <c r="T17" s="4" t="n">
-        <v>2024</v>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="U17" s="11" t="inlineStr">
         <is>
           <t>Static</t>
         </is>
       </c>
-      <c r="V17" s="21" t="inlineStr">
+      <c r="V17" s="10" t="inlineStr">
         <is>
           <t>https://github.com/core-stack-org/QGIS-Styles/blob/main/Hydrology/Sub-Basin_style.qml</t>
         </is>
@@ -4102,9 +4150,8 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Core Stack (Open access)
-Sudharsan Malaiappan - s.maliappan@cgiar.org
-</t>
+          <t>Core Stack (Open access)
+Sudharsan Malaiappan - s.maliappan@cgiar.org</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
@@ -4136,15 +4183,17 @@
         </is>
       </c>
       <c r="S18" s="5" t="n"/>
-      <c r="T18" s="4" t="n">
-        <v>2025</v>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="U18" s="11" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="V18" s="22" t="inlineStr">
+      <c r="V18" s="21" t="inlineStr">
         <is>
           <t>https://github.com/core-stack-org/QGIS-Styles/blob/main/Land/LULC0_12class.qml</t>
         </is>
@@ -4153,60 +4202,108 @@
     <row r="19" ht="21.75" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-016</t>
+          <t>MFL-2026-017</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Groundwater data - India</t>
+          <t>Land Use and Land Cover - Senegal</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Water / hydrology</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>IND-CH — Central India Highlands</t>
+          <t>SEN-FK — Fatick Department</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>ISRA-BAME</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>dieyemohamadou@gmail.com</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
       <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n"/>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="4" t="n"/>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>Land cover derived from Sentinel-2 imagery using machine learning classification. Moderate spatial accuracy depending on land cover type and cloud cover; small or rapid changes may not be captured. Related: Sentinel-2 imagery, global land cover datasets, NDVI products.</t>
+        </is>
+      </c>
       <c r="S19" s="5" t="n"/>
-      <c r="T19" s="4" t="n"/>
-      <c r="U19" s="11" t="n"/>
-      <c r="V19" s="10" t="n"/>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U19" s="11" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="V19" s="10" t="inlineStr">
+        <is>
+          <t>https://livingatlas.arcgis.com/landcoverexplorer/#mapCenter=-14.06266%2C13.65709%2C11.00&amp;mode=step&amp;timeExtent=2017%2C2022&amp;year=2023</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="21.75" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-017</t>
+          <t>MFL-2026-018</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Land Use and Land Cover - Senegal</t>
+          <t>Departments</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -4216,7 +4313,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Boundaries / admin units</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -4226,27 +4323,19 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Raster</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>2017-2025</t>
-        </is>
-      </c>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>ISRA-BAME</t>
         </is>
       </c>
-      <c r="J20" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dieyemohamadou@gmail.com </t>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>dieyemohamadou@gmail.com</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -4256,7 +4345,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -4274,33 +4363,31 @@
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Land cover derived from Sentinel-2 imagery using machine learning classification. Moderate spatial accuracy depending on land cover type and cloud cover; small or rapid changes may not be captured. Related: Sentinel-2 imagery, global land cover datasets, NDVI products.</t>
+          <t>Official administrative boundaries of Senegal</t>
         </is>
       </c>
       <c r="S20" s="5" t="n"/>
-      <c r="T20" s="4" t="n">
-        <v>2025</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
       <c r="U20" s="11" t="inlineStr">
         <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="V20" s="22" t="inlineStr">
-        <is>
-          <t>https://livingatlas.arcgis.com/landcoverexplorer/#mapCenter=-14.06266%2C13.65709%2C11.00&amp;mode=step&amp;timeExtent=2017%2C2022&amp;year=2023</t>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V20" s="21" t="inlineStr">
+        <is>
+          <t>https://gadm.org/</t>
         </is>
       </c>
     </row>
     <row r="21" ht="21.75" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-018</t>
+          <t>MFL-2026-019</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Departments </t>
+          <t>Municipalities</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -4330,9 +4417,9 @@
           <t>ISRA-BAME</t>
         </is>
       </c>
-      <c r="J21" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dieyemohamadou@gmail.com </t>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>dieyemohamadou@gmail.com</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -4342,7 +4429,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -4364,12 +4451,13 @@
         </is>
       </c>
       <c r="S21" s="5" t="n"/>
+      <c r="T21" s="4" t="n"/>
       <c r="U21" s="11" t="inlineStr">
         <is>
           <t>Static</t>
         </is>
       </c>
-      <c r="V21" s="22" t="inlineStr">
+      <c r="V21" s="10" t="inlineStr">
         <is>
           <t>https://gadm.org/</t>
         </is>
@@ -4378,12 +4466,12 @@
     <row r="22" ht="21.75" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-019</t>
+          <t>MFL-2026-020</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Municipalities</t>
+          <t>Localities</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -4413,9 +4501,9 @@
           <t>ISRA-BAME</t>
         </is>
       </c>
-      <c r="J22" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dieyemohamadou@gmail.com </t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>dieyemohamadou@gmail.com</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
@@ -4453,21 +4541,17 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="V22" s="22" t="inlineStr">
-        <is>
-          <t>https://gadm.org/</t>
-        </is>
-      </c>
+      <c r="V22" s="21" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-020</t>
+          <t>MFL-2026-021</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Localities</t>
+          <t>Road</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -4497,9 +4581,9 @@
           <t>ISRA-BAME</t>
         </is>
       </c>
-      <c r="J23" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dieyemohamadou@gmail.com </t>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>dieyemohamadou@gmail.com</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -4509,7 +4593,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -4537,17 +4621,21 @@
           <t>Static</t>
         </is>
       </c>
-      <c r="V23" s="10" t="n"/>
+      <c r="V23" s="10" t="inlineStr">
+        <is>
+          <t>https://gadm.org/</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="21.75" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-021</t>
+          <t>MFL-2026-022</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Road</t>
+          <t>Land Degradation - Senegal</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -4557,7 +4645,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -4567,19 +4655,27 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>500m</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>2000 - 2024</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
           <t>ISRA-BAME</t>
         </is>
       </c>
-      <c r="J24" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dieyemohamadou@gmail.com </t>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>dieyemohamadou@gmail.com</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -4594,44 +4690,48 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Processed</t>
         </is>
       </c>
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>local</t>
         </is>
       </c>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>Official administrative boundaries of Senegal</t>
+          <t>Based on MODIS time-series vegetation indices (NDVI/EVI) to assess land condition. Coarse spatial resolution (250m–1km) and atmospheric/cloud effects may limit precision; short-term changes may be smoothed. Related: Landsat, Sentinel-2, soil and climate datasets. — Original landscape entry: In the Senegal region, the resolution does not allow for data at the departmental level</t>
         </is>
       </c>
       <c r="S24" s="5" t="n"/>
-      <c r="T24" s="4" t="n"/>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="U24" s="11" t="inlineStr">
         <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="V24" s="22" t="inlineStr">
-        <is>
-          <t>https://gadm.org/</t>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="V24" s="21" t="inlineStr">
+        <is>
+          <t>Plugin Trends earth</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30.75" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-022</t>
+          <t>MFL-2026-023</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Land Degradation - Senegal</t>
+          <t>Tree mapping</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -4641,7 +4741,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -4651,17 +4751,13 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Raster</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>500m</t>
-        </is>
-      </c>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>2000 - 2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -4669,9 +4765,9 @@
           <t>ISRA-BAME</t>
         </is>
       </c>
-      <c r="J25" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dieyemohamadou@gmail.com </t>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>dieyemohamadou@gmail.com</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -4686,46 +4782,40 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="N25" s="4" t="n"/>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Drive</t>
         </is>
       </c>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="inlineStr">
         <is>
-          <t>Based on MODIS time-series vegetation indices (NDVI/EVI) to assess land condition. Coarse spatial resolution (250m–1km) and atmospheric/cloud effects may limit precision; short-term changes may be smoothed. Related: Landsat, Sentinel-2, soil and climate datasets. — Original landscape entry: In the Senegal region, the resolution does not allow for data at the departmental level</t>
+          <t>Tree data are derived from Sentinel-2 imagery using image classification techniques. Limitations include infrequent updates, which may affect temporal accuracy and may not reflect recent changes. Related datasets: Sentinel-2 imagery, land cover products, vegetation indices (NDVI/EVI).</t>
         </is>
       </c>
       <c r="S25" s="5" t="n"/>
-      <c r="T25" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="U25" s="11" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="V25" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Plugin Trends earth </t>
-        </is>
-      </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="U25" s="11" t="n"/>
+      <c r="V25" s="10" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-023</t>
+          <t>MFL-2026-024</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Tree mapping</t>
+          <t>Rainfall data</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -4735,7 +4825,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Water / hydrology</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -4745,21 +4835,23 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n">
-        <v>2021</v>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>1981 – présent</t>
+        </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
           <t>ISRA-BAME</t>
         </is>
       </c>
-      <c r="J26" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dieyemohamadou@gmail.com </t>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>dieyemohamadou@gmail.com</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -4774,52 +4866,63 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Processed</t>
         </is>
       </c>
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>local</t>
         </is>
       </c>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="inlineStr">
         <is>
-          <t>Tree data are derived from Sentinel-2 imagery using image classification techniques. Limitations include infrequent updates, which may affect temporal accuracy and may not reflect recent changes. Related datasets: Sentinel-2 imagery, land cover products, vegetation indices (NDVI/EVI).</t>
+          <t>Derived from satellite observations and climate models (reanalysis and gauge integration). Coarse spatial resolution (~0.25°–1°) and potential bias compared to ground stations; local variability may be underestimated. Related: GPM, TRMM, ERA5, meteorological station data.</t>
         </is>
       </c>
       <c r="S26" s="5" t="n"/>
-      <c r="T26" s="4" t="n">
-        <v>2021</v>
-      </c>
-      <c r="U26" s="11" t="n"/>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U26" s="11" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="V26" s="21" t="inlineStr">
+        <is>
+          <t>https://power.larc.nasa.gov/data-access-viewer/</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="33.75" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-024</t>
+          <t>MFL-2026-025</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Rainfall data</t>
+          <t>Crop damage mapping</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Water / hydrology</t>
+          <t>Ecosystem services</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>SEN-FK — Fatick Department</t>
+          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -4827,20 +4930,24 @@
           <t>Tabular</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Ward level</t>
+        </is>
+      </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1981 – présent </t>
+          <t>2025 -2026</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>ISRA-BAME</t>
-        </is>
-      </c>
-      <c r="J27" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dieyemohamadou@gmail.com </t>
+          <t>CIMMYT</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Telma.SIBANDA@um6p.ma</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -4850,91 +4957,89 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>CGIAR Open Access</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>Drive</t>
         </is>
       </c>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="inlineStr">
         <is>
-          <t>Derived from satellite observations and climate models (reanalysis and gauge integration). Coarse spatial resolution (~0.25°–1°) and potential bias compared to ground stations; local variability may be underestimated. Related: GPM, TRMM, ERA5, meteorological station data.</t>
+          <t>Ward-level crop damage data (severity and incidence) by different species — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
         </is>
       </c>
       <c r="S27" s="5" t="n"/>
-      <c r="T27" s="4" t="n">
-        <v>2025</v>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U27" s="11" t="inlineStr">
         <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="V27" s="15" t="inlineStr">
-        <is>
-          <t>https://power.larc.nasa.gov/data-access-viewer/</t>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="V27" s="10" t="inlineStr">
+        <is>
+          <t>Internal Available on request</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-064</t>
+          <t>MFL-2026-026</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Tree conservation and restoration priority areas</t>
+          <t>District/ward boundaries</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Decision-support outputs</t>
+          <t>Boundaries / admin units</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>NATIONAL — Country-wide coverage</t>
+          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Raster</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>1000m</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>2017-2025</t>
-        </is>
-      </c>
+          <t>Admin - MFLLs Boundary</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Alliance Bioversity-CIAT</t>
-        </is>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>Hannes Gaisberger, h.gaisberger@cgiar.org</t>
+          <t>CIMMYT</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Telma.SIBANDA@um6p.ma</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -4944,7 +5049,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>CGIAR Open Access</t>
+          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -4955,45 +5060,38 @@
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>Dataverse repository</t>
+          <t>Drive</t>
         </is>
       </c>
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="inlineStr">
         <is>
-          <t>Conservation for Restoration (C4R) tool KENYA: mapping the vulnerability and priority areas for conservation and restoration of 78 native tree species. Linked to D4R</t>
+          <t>Administrative boundaries for the Lower Zambezi Valley (Districts and wards)</t>
         </is>
       </c>
       <c r="S28" s="5" t="n"/>
-      <c r="T28" s="4" t="n">
-        <v>2025</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
       <c r="U28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">On-demand </t>
-        </is>
-      </c>
-      <c r="V28" s="15" t="inlineStr">
-        <is>
-          <t>https://dataverse.harvard.edu/citation?persistentId=doi:10.7910/DVN/2ZQTB2</t>
-        </is>
-      </c>
-      <c r="W28" s="20" t="inlineStr">
-        <is>
-          <t>220 MB</t>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V28" s="21" t="inlineStr">
+        <is>
+          <t>https://gadm.org/</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21.75" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-065</t>
+          <t>MFL-2026-027</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Soil health status and texture</t>
+          <t>LULC classification</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -5003,7 +5101,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -5013,23 +5111,25 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Ward level</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>2024</v>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
           <t>CIMMYT</t>
         </is>
       </c>
-      <c r="J29" s="23" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>Telma.SIBANDA@um6p.ma</t>
         </is>
@@ -5046,7 +5146,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="N29" s="4" t="n"/>
@@ -5059,19 +5159,21 @@
       <c r="Q29" s="4" t="n"/>
       <c r="R29" s="4" t="inlineStr">
         <is>
-          <t>Ward-level soil texture, nitrogen, and carbon content data — Original landscape entry: Mbire: Wards 2 and 3</t>
+          <t>Land Use and Land Cover Classification — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
         </is>
       </c>
       <c r="S29" s="5" t="n"/>
-      <c r="T29" s="4" t="n">
-        <v>2024</v>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U29" s="11" t="inlineStr">
         <is>
           <t>Static</t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
+      <c r="V29" s="10" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
         </is>
@@ -5080,12 +5182,12 @@
     <row r="30" ht="21.75" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-025</t>
+          <t>MFL-2026-028</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crop damage mapping </t>
+          <t>LULC classification training points</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -5095,7 +5197,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Ecosystem services</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -5110,12 +5212,12 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Ward level</t>
+          <t>10m</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>2025 -2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -5123,7 +5225,7 @@
           <t>CIMMYT</t>
         </is>
       </c>
-      <c r="J30" s="15" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr">
         <is>
           <t>Telma.SIBANDA@um6p.ma</t>
         </is>
@@ -5140,7 +5242,7 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="N30" s="4" t="n"/>
@@ -5153,19 +5255,21 @@
       <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="inlineStr">
         <is>
-          <t>Ward-level crop damage data (severity and incidence) by different species — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
+          <t>Land Use and Land Cover Classification training points from Sentinel 2 — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
         </is>
       </c>
       <c r="S30" s="5" t="n"/>
-      <c r="T30" s="4" t="n">
-        <v>2026</v>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="U30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seasonal </t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V30" s="21" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
         </is>
@@ -5174,12 +5278,12 @@
     <row r="31" ht="21.75" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-026</t>
+          <t>MFL-2026-029</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>District/ward boundaries</t>
+          <t>Ecosystem services mapping</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -5189,7 +5293,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
+          <t>Ecosystem services</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -5199,21 +5303,21 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>Admin - MFLLs Boundary</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="n"/>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>CIMMYT</t>
-        </is>
-      </c>
-      <c r="J31" s="23" t="inlineStr">
+          <t>IWMI</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
         <is>
           <t>Telma.SIBANDA@um6p.ma</t>
         </is>
@@ -5230,7 +5334,7 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Processed</t>
         </is>
       </c>
       <c r="N31" s="4" t="n"/>
@@ -5243,69 +5347,75 @@
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>Administrative boundaries for the Lower Zambezi Valley (Districts and wards)</t>
+          <t>Ward-level ecosystem services mapping — Original landscape entry: Mbire Ward 2</t>
         </is>
       </c>
       <c r="S31" s="5" t="n"/>
-      <c r="T31" s="4" t="n"/>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="U31" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V31" s="15" t="inlineStr">
-        <is>
-          <t>https://gadm.org/</t>
+      <c r="V31" s="10" t="inlineStr">
+        <is>
+          <t>Internal Available on request</t>
         </is>
       </c>
     </row>
     <row r="32" ht="21.75" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-027</t>
+          <t>MFL-2026-030</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>LULC classification</t>
+          <t>Tunisia LLs Governorate boundary for Le Kef and Siliana.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Boundaries / admin units</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
+          <t>TUN-NW — Northwestern Tunisia</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Raster</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>2026</v>
+          <t>admin-level-1</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>CIMMYT</t>
-        </is>
-      </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>Telma.SIBANDA@um6p.ma</t>
+          <t>ICARDA</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Layal Atassi - l.atassi@cgiar.org</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
@@ -5333,71 +5443,67 @@
       <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="inlineStr">
         <is>
-          <t>Land Use and Land Cover Classification — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
+          <t>Administrative boundaries for Tunisia</t>
         </is>
       </c>
       <c r="S32" s="5" t="n"/>
-      <c r="T32" s="4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U32" s="11" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>Internal Available on request</t>
+      <c r="T32" s="4" t="n"/>
+      <c r="U32" s="11" t="n"/>
+      <c r="V32" s="21" t="inlineStr">
+        <is>
+          <t>www.geoboundaries.org</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21.75" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-028</t>
+          <t>MFL-2026-031</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>LULC classification training points</t>
+          <t>Tunisia LLs Sector boundary containing Es Sers, Gaafour, El Krib, Makthar, and Kesra.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Boundaries / admin units</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
+          <t>TUN-NW — Northwestern Tunisia</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>10m</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>2026</v>
+          <t>admin-level-2</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>CIMMYT</t>
-        </is>
-      </c>
-      <c r="J33" s="23" t="inlineStr">
-        <is>
-          <t>Telma.SIBANDA@um6p.ma</t>
+          <t>ICARDA</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Layal Atassi - l.atassi@cgiar.org</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -5425,67 +5531,67 @@
       <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="inlineStr">
         <is>
-          <t>Land Use and Land Cover Classification training points from Sentinel 2 — Original landscape entry: Mbire: Wards 2, 3, 9, 12 and 17</t>
+          <t>Administrative boundaries for Tunisia</t>
         </is>
       </c>
       <c r="S33" s="5" t="n"/>
-      <c r="T33" s="4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U33" s="11" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>Internal Available on request</t>
+      <c r="T33" s="4" t="n"/>
+      <c r="U33" s="11" t="n"/>
+      <c r="V33" s="10" t="inlineStr">
+        <is>
+          <t>www.geoboundaries.org</t>
         </is>
       </c>
     </row>
     <row r="34" ht="21.75" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-029</t>
+          <t>MFL-2026-032</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Ecosystem services mapping</t>
+          <t>Tunisia LLs boundary for the six communities containing Sers, Elles, El Ahouez Sud, Hammam Biadha Sud, Chouarnia, and Kesra.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Ecosystem services</t>
+          <t>Boundaries / admin units</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
+          <t>TUN-NW — Northwestern Tunisia</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Mixed</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n">
-        <v>2026</v>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>admin-level-3</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>IWMI</t>
-        </is>
-      </c>
-      <c r="J34" s="23" t="inlineStr">
-        <is>
-          <t>Telma.SIBANDA@um6p.ma</t>
+          <t>ICARDA</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Layal Atassi - l.atassi@cgiar.org</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
@@ -5500,7 +5606,7 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="N34" s="4" t="n"/>
@@ -5513,33 +5619,27 @@
       <c r="Q34" s="4" t="n"/>
       <c r="R34" s="4" t="inlineStr">
         <is>
-          <t>Ward-level ecosystem services mapping — Original landscape entry: Mbire Ward 2</t>
+          <t>Administrative boundaries for Tunisia</t>
         </is>
       </c>
       <c r="S34" s="5" t="n"/>
-      <c r="T34" s="4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U34" s="11" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>Internal Available on request</t>
+      <c r="T34" s="4" t="n"/>
+      <c r="U34" s="11" t="n"/>
+      <c r="V34" s="21" t="inlineStr">
+        <is>
+          <t>www.geoboundaries.org</t>
         </is>
       </c>
     </row>
     <row r="35" ht="21.75" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-030</t>
+          <t>MFL-2026-033</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Tunisia LLs Governorate boundary for Le Kef and Siliana.</t>
+          <t>Tunisia Land use land cover for Le Kef and Siliana.</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -5549,7 +5649,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -5564,12 +5664,12 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>admin-level-1</t>
+          <t>10 m</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -5579,7 +5679,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Layal Atassi - l.atassi@cgiar.org</t>
+          <t>Ayman Frija -  a.frija@cgiar.org</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -5607,27 +5707,31 @@
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="inlineStr">
         <is>
-          <t>Administrative boundaries for Tunisia</t>
+          <t>Land Use and Land Cover Classification</t>
         </is>
       </c>
       <c r="S35" s="5" t="n"/>
-      <c r="T35" s="4" t="n"/>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U35" s="11" t="n"/>
-      <c r="V35" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> www.geoboundaries.org</t>
+      <c r="V35" s="10" t="inlineStr">
+        <is>
+          <t>Internal Available on request</t>
         </is>
       </c>
     </row>
     <row r="36" ht="21.75" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-031</t>
+          <t>MFL-2026-034</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Tunisia LLs Sector boundary containing Es Sers, Gaafour, El Krib, Makthar, and Kesra.</t>
+          <t>Tunisia Agricultural soil for Le Kef and Siliana.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -5637,10 +5741,10 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
-        </is>
-      </c>
-      <c r="E36" s="25" t="inlineStr">
+          <t>Degradation / land health</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>TUN-NW — Northwestern Tunisia</t>
         </is>
@@ -5650,14 +5754,10 @@
           <t>Vector</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>admin-level-2</t>
-        </is>
-      </c>
+      <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -5667,7 +5767,7 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Layal Atassi - l.atassi@cgiar.org</t>
+          <t>Ayman Frija -  a.frija@cgiar.org</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -5695,27 +5795,31 @@
       <c r="Q36" s="4" t="n"/>
       <c r="R36" s="4" t="inlineStr">
         <is>
-          <t>Administrative boundaries for Tunisia</t>
+          <t>Agricultural soil map classification</t>
         </is>
       </c>
       <c r="S36" s="5" t="n"/>
-      <c r="T36" s="4" t="n"/>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
       <c r="U36" s="11" t="n"/>
-      <c r="V36" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> www.geoboundaries.org</t>
+      <c r="V36" s="21" t="inlineStr">
+        <is>
+          <t>Internal Available on request</t>
         </is>
       </c>
     </row>
     <row r="37" ht="21.75" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-032</t>
+          <t>MFL-2026-035</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Tunisia LLs boundary for the six communities containing Sers, Elles, El Ahouez Sud, Hammam Biadha Sud, Chouarnia, and Kesra.</t>
+          <t>Agroecological and socioeconomic datasets</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -5725,27 +5829,23 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
-        </is>
-      </c>
-      <c r="E37" s="25" t="inlineStr">
+          <t>Socio-economic / livelihoods</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>TUN-NW — Northwestern Tunisia</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>admin-level-3</t>
-        </is>
-      </c>
+          <t>Tabular</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -5755,24 +5855,12 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>Layal Atassi - l.atassi@cgiar.org</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>CGIAR Open Access</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>Validated</t>
-        </is>
-      </c>
+          <t>Ayman Frija -  a.frija@cgiar.org</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="inlineStr">
         <is>
@@ -5783,42 +5871,46 @@
       <c r="Q37" s="4" t="n"/>
       <c r="R37" s="4" t="inlineStr">
         <is>
-          <t>Administrative boundaries for Tunisia</t>
+          <t>Survay collecting evidence of the holistic impact of agroecology</t>
         </is>
       </c>
       <c r="S37" s="5" t="n"/>
       <c r="T37" s="4" t="n"/>
-      <c r="U37" s="11" t="n"/>
-      <c r="V37" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> www.geoboundaries.org</t>
+      <c r="U37" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V37" s="10" t="inlineStr">
+        <is>
+          <t>Internal Available on request</t>
         </is>
       </c>
     </row>
     <row r="38" ht="21.75" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-033</t>
+          <t>MFL-2026-036</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Tunisia Land use land cover for Le Kef and Siliana.</t>
+          <t>Agricultural production system</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Socio-economic / livelihoods</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>TUN-NW — Northwestern Tunisia</t>
+          <t>ETH-OG — Omo-Gibe Basin</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -5826,22 +5918,20 @@
           <t>Vector</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>10 m</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>2021</v>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>ICARDA</t>
+          <t>NASA / USGS (external)</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Ayman Frija -  a.frija@cgiar.org</t>
+          <t>Degefie Tibebe- d.tibebe@cgiar.org</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
@@ -5851,12 +5941,12 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>CGIAR Open Access</t>
+          <t>Restricted — contact data owner</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Raw</t>
         </is>
       </c>
       <c r="N38" s="4" t="n"/>
@@ -5869,15 +5959,13 @@
       <c r="Q38" s="4" t="n"/>
       <c r="R38" s="4" t="inlineStr">
         <is>
-          <t>Land Use and Land Cover Classification</t>
+          <t>Survey</t>
         </is>
       </c>
       <c r="S38" s="5" t="n"/>
-      <c r="T38" s="4" t="n">
-        <v>2021</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
       <c r="U38" s="11" t="n"/>
-      <c r="V38" s="8" t="inlineStr">
+      <c r="V38" s="21" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
         </is>
@@ -5886,56 +5974,58 @@
     <row r="39" ht="21.75" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-034</t>
+          <t>MFL-2026-037</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Tunisia Agricultural soil for Le Kef and Siliana.</t>
+          <t>Land use/cover</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>TUN-NW — Northwestern Tunisia</t>
+          <t>ETH-OG — Omo-Gibe Basin</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n">
-        <v>2021</v>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>ICARDA</t>
-        </is>
-      </c>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>30 m</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>Ayman Frija -  a.frija@cgiar.org</t>
+          <t>Degefie Tibebe- d.tibebe@cgiar.org</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Restricted</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>CGIAR Open Access</t>
+          <t>Restricted — contact data owner</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -5953,15 +6043,17 @@
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="inlineStr">
         <is>
-          <t>Agricultural soil map classification</t>
+          <t>Land Use and Land Cover Classification</t>
         </is>
       </c>
       <c r="S39" s="5" t="n"/>
-      <c r="T39" s="4" t="n">
-        <v>2021</v>
-      </c>
-      <c r="U39" s="11" t="n"/>
-      <c r="V39" s="8" t="inlineStr">
+      <c r="T39" s="4" t="n"/>
+      <c r="U39" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V39" s="10" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
         </is>
@@ -5970,51 +6062,69 @@
     <row r="40" ht="21.75" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-035</t>
+          <t>MFL-2026-038</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agroecological and socioeconomic datasets </t>
+          <t>Soil resource</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Socio-economic / livelihoods</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>TUN-NW — Northwestern Tunisia</t>
+          <t>ETH-OG — Omo-Gibe Basin</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Tabular</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n">
-        <v>2024</v>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>250 m</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>ICARDA</t>
+          <t>Alliance Bioversity-CIAT</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>Ayman Frija -  a.frija@cgiar.org</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
-      <c r="M40" s="4" t="n"/>
+          <t>Degefie Tibebe- d.tibebe@cgiar.org</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>Restricted — contact data owner</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="inlineStr">
         <is>
@@ -6025,17 +6135,17 @@
       <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="inlineStr">
         <is>
-          <t>Survay collecting evidence of the holistic impact of agroecology</t>
+          <t>Digital soil mapping</t>
         </is>
       </c>
       <c r="S40" s="5" t="n"/>
       <c r="T40" s="4" t="n"/>
-      <c r="U40" s="8" t="inlineStr">
+      <c r="U40" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V40" s="8" t="inlineStr">
+      <c r="V40" s="21" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
         </is>
@@ -6044,12 +6154,12 @@
     <row r="41" ht="21.75" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-036</t>
+          <t>MFL-2026-039</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Agricultural production system</t>
+          <t>District level crop area, prodcution and yield data - India</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -6059,7 +6169,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Socio-economic / livelihoods</t>
+          <t>Agrobiodiversity / crops</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -6069,16 +6179,18 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n">
-        <v>2018</v>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>1991-2020</t>
+        </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>NASA / USGS (external)</t>
+          <t>National government (external)</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -6093,12 +6205,12 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>Restricted — contact data owner</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>Validated</t>
         </is>
       </c>
       <c r="N41" s="4" t="n"/>
@@ -6111,12 +6223,17 @@
       <c r="Q41" s="4" t="n"/>
       <c r="R41" s="4" t="inlineStr">
         <is>
-          <t>Survey</t>
+          <t>District level crop area, production and yield.</t>
         </is>
       </c>
       <c r="S41" s="5" t="n"/>
       <c r="T41" s="4" t="n"/>
-      <c r="V41" s="8" t="inlineStr">
+      <c r="U41" s="11" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="V41" s="10" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
         </is>
@@ -6125,12 +6242,12 @@
     <row r="42" ht="21.75" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-037</t>
+          <t>MFL-2026-040</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Land use/cover</t>
+          <t>Agroecological zones</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -6138,11 +6255,7 @@
           <t>Ethiopia</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>Land cover / land use</t>
-        </is>
-      </c>
+      <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="inlineStr">
         <is>
           <t>ETH-OG — Omo-Gibe Basin</t>
@@ -6150,18 +6263,20 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Raster</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>30 m</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>2021</v>
-      </c>
-      <c r="I42" s="4" t="n"/>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>National government (external)</t>
+        </is>
+      </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
           <t>Degefie Tibebe- d.tibebe@cgiar.org</t>
@@ -6169,12 +6284,12 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>Restricted</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>Restricted — contact data owner</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
@@ -6192,17 +6307,17 @@
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="inlineStr">
         <is>
-          <t>Land Use and Land Cover Classification</t>
-        </is>
-      </c>
-      <c r="S42" s="5" t="n"/>
+          <t>Agroecological zonations</t>
+        </is>
+      </c>
+      <c r="S42" s="5" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
       <c r="T42" s="4" t="n"/>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
+      <c r="U42" s="11" t="n"/>
+      <c r="V42" s="21" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
         </is>
@@ -6211,12 +6326,12 @@
     <row r="43" ht="21.75" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-038</t>
+          <t>MFL-2026-041</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Soil resource</t>
+          <t>Experimental CSA practices</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -6226,7 +6341,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Biodiversity / ecosystems</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -6236,16 +6351,14 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Raster</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>250 m</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>2024</v>
+          <t>Tabular</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>2000-2020</t>
+        </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -6264,7 +6377,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>Restricted — contact data owner</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
@@ -6282,17 +6395,21 @@
       <c r="Q43" s="4" t="n"/>
       <c r="R43" s="4" t="inlineStr">
         <is>
-          <t>Digital soil mapping</t>
-        </is>
-      </c>
-      <c r="S43" s="5" t="n"/>
+          <t>Agroecological zonations</t>
+        </is>
+      </c>
+      <c r="S43" s="5" t="inlineStr">
+        <is>
+          <t>Drive</t>
+        </is>
+      </c>
       <c r="T43" s="4" t="n"/>
-      <c r="U43" s="8" t="inlineStr">
+      <c r="U43" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V43" s="8" t="inlineStr">
+      <c r="V43" s="10" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
         </is>
@@ -6301,12 +6418,12 @@
     <row r="44" ht="21.75" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-039</t>
+          <t>MFL-2026-042</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>District level crop area, prodcution and yield data - India</t>
+          <t>Erosion map</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -6316,7 +6433,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Agrobiodiversity / crops</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -6326,13 +6443,13 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>1991-2020</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -6370,17 +6487,17 @@
       <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="inlineStr">
         <is>
-          <t>District level crop area, production and yield.</t>
+          <t>Emprical modellling</t>
         </is>
       </c>
       <c r="S44" s="5" t="n"/>
       <c r="T44" s="4" t="n"/>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
+      <c r="U44" s="11" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V44" s="21" t="inlineStr">
         <is>
           <t>Internal Available on request</t>
         </is>
@@ -6389,23 +6506,27 @@
     <row r="45" ht="21.75" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-040</t>
+          <t>MFL-2026-044</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Agroecological zones</t>
+          <t>District/Region boundaries</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="n"/>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>ETH-OG — Omo-Gibe Basin</t>
+          <t>CIV-NZ — N'Zi Watershed</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -6413,9 +6534,15 @@
           <t>Vector</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n">
-        <v>2005</v>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>admin-level-1, admin-level-2, admin-level-3</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
@@ -6424,7 +6551,7 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Degefie Tibebe- d.tibebe@cgiar.org</t>
+          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -6434,7 +6561,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Restricted — GADM terms (academic/non-commercial use only, no redistribution)</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -6452,66 +6579,63 @@
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="inlineStr">
         <is>
-          <t>Agroecological zonations</t>
-        </is>
-      </c>
-      <c r="S45" s="4" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
+          <t>Administrative boundaries</t>
+        </is>
+      </c>
+      <c r="S45" s="5" t="n"/>
       <c r="T45" s="4" t="n"/>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>Internal Available on request</t>
+      <c r="U45" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V45" s="10" t="inlineStr">
+        <is>
+          <t>GADM maps and data (gadm.org)</t>
         </is>
       </c>
     </row>
     <row r="46" ht="21.75" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-041</t>
+          <t>MFL-2026-045</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Experimental CSA practices</t>
+          <t>Agroecological zones</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>Biodiversity / ecosystems</t>
-        </is>
-      </c>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>ETH-OG — Omo-Gibe Basin</t>
+          <t>CIV-NZ — N'Zi Watershed</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>2000-2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Alliance Bioversity-CIAT</t>
+          <t>IFPRI</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>Degefie Tibebe- d.tibebe@cgiar.org</t>
+          <t>Justin Djagba (j.djagba@cgiar.org)</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
@@ -6521,7 +6645,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Other (specify in notes)</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
@@ -6539,71 +6663,75 @@
       <c r="Q46" s="4" t="n"/>
       <c r="R46" s="4" t="inlineStr">
         <is>
-          <t>Agroecological zonations</t>
-        </is>
-      </c>
-      <c r="S46" s="4" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
-      <c r="T46" s="4" t="n"/>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>Internal Available on request</t>
+          <t>Agroecological zones</t>
+        </is>
+      </c>
+      <c r="S46" s="5" t="n"/>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="U46" s="11" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V46" s="21" t="inlineStr">
+        <is>
+          <t>HarvestChoice, International Food Policy Research Institute (IFPRI); University of Minnesota, 2017, "CELL5M: A Multidisciplinary Geospatial Database for Africa South of the Sahara", https://doi.org/10.7910/DVN/G4TBLF, Harvard Dataverse, V5</t>
         </is>
       </c>
     </row>
     <row r="47" ht="21.75" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-042</t>
+          <t>MFL-2026-046</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Erosion map</t>
+          <t>Climate station data (NHMS synoptic stations)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Water / hydrology</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>ETH-OG — Omo-Gibe Basin</t>
+          <t>CIV-NZ — N'Zi Watershed</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Raster</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="n"/>
+          <t>Tabular</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Climate station observations</t>
+        </is>
+      </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>since 2014</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>National government (external)</t>
+          <t>AfricaRice</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Degefie Tibebe- d.tibebe@cgiar.org</t>
+          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -6613,7 +6741,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Other (specify in notes)</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -6624,85 +6752,139 @@
       <c r="N47" s="4" t="n"/>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>server and drive</t>
         </is>
       </c>
       <c r="P47" s="4" t="n"/>
       <c r="Q47" s="4" t="n"/>
       <c r="R47" s="4" t="inlineStr">
         <is>
-          <t>Emprical modellling</t>
+          <t>Climate data from climate stations for three major cities in the watershed (coverage period varies depending on the station); climate data from M'Be research station</t>
         </is>
       </c>
       <c r="S47" s="5" t="n"/>
-      <c r="T47" s="4" t="n"/>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>Internal Available on request</t>
+      <c r="T47" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U47" s="11" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="V47" s="10" t="inlineStr">
+        <is>
+          <t>NHMS for the synoptic climate stations</t>
         </is>
       </c>
     </row>
     <row r="48" ht="21.75" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-043</t>
+          <t>MFL-2026-048</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Rainfall trends</t>
+          <t>DSSAT soil profiles (global .SOL files)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Water / hydrology</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>NATIONAL — Country-wide coverage</t>
+          <t>GLOBAL — Global / cross-landscape</t>
         </is>
       </c>
       <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="n"/>
-      <c r="L48" s="4" t="n"/>
-      <c r="M48" s="4" t="n"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>5-min resolution</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>AfricaRice</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
       <c r="N48" s="4" t="n"/>
-      <c r="O48" s="4" t="n"/>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>server and drive</t>
+        </is>
+      </c>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
-      <c r="R48" s="4" t="n"/>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>High-resolution soil profile database for crop modeling applications. Files are '*.SOL' file format (DSSAT soil database) for each country worldwide.</t>
+        </is>
+      </c>
       <c r="S48" s="5" t="n"/>
-      <c r="T48" s="4" t="n"/>
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="U48" s="11" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V48" s="21" t="inlineStr">
+        <is>
+          <t>International Research Institute for Climate and Society (IRI); Michigan State University (MSU); HarvestChoice, International Food Policy Research Institute (IFPRI), 2015, "Global High-Resolution Soil Profile Database for Crop Modeling Applications", https://doi.org/10.7910/DVN/1PEEY0</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="27" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-044</t>
+          <t>MFL-2026-050</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>District/Region boundaries</t>
+          <t>watershed boundary</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -6712,7 +6894,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>CIV-NZ — N'Zi Watershed</t>
+          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -6722,32 +6904,32 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>admin-level-1, admin-level-2, admin-level-3</t>
+          <t>basin and country levels</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>present</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>National government (external)</t>
+          <t>IWMI</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
+          <t>s.douangsavanh@cgiar.org</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Restricted — contact data owner</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -6758,78 +6940,96 @@
       <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>server and drive</t>
         </is>
       </c>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="inlineStr">
         <is>
-          <t>Administrative boundaries</t>
-        </is>
-      </c>
-      <c r="S49" s="5" t="n"/>
-      <c r="T49" s="4" t="n"/>
-      <c r="U49" s="8" t="inlineStr">
+          <t>MRC produced the data</t>
+        </is>
+      </c>
+      <c r="S49" s="5" t="inlineStr">
+        <is>
+          <t>MRC produced the data</t>
+        </is>
+      </c>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U49" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>GADM maps and data (gadm.org)</t>
+      <c r="V49" s="10" t="inlineStr">
+        <is>
+          <t>MRC website</t>
         </is>
       </c>
     </row>
     <row r="50" ht="39.75" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-045</t>
+          <t>MFL-2026-051</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Agroecological zones</t>
+          <t>river network</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="n"/>
+          <t>Laos</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>Water / hydrology</t>
+        </is>
+      </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>CIV-NZ — N'Zi Watershed</t>
+          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Raster</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n">
-        <v>2017</v>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>basin and country levels</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>IFPRI</t>
+          <t>IWMI</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Justin Djagba (j.djagba@cgiar.org)</t>
+          <t>s.douangsavanh@cgiar.org</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Restricted — contact data owner</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
@@ -6840,90 +7040,96 @@
       <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>Drive</t>
+          <t>server and drive</t>
         </is>
       </c>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="inlineStr">
         <is>
-          <t>Agroecological zones</t>
-        </is>
-      </c>
-      <c r="S50" s="5" t="n"/>
-      <c r="T50" s="4" t="n">
-        <v>2017</v>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="V50" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HarvestChoice, International Food Policy Research Institute (IFPRI); University of Minnesota, 2017, "CELL5M: A Multidisciplinary Geospatial Database for Africa South of the Sahara", https://doi.org/10.7910/DVN/G4TBLF, Harvard Dataverse, V5 </t>
+          <t>MRC produced the data</t>
+        </is>
+      </c>
+      <c r="S50" s="5" t="inlineStr">
+        <is>
+          <t>MRC produced the data</t>
+        </is>
+      </c>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U50" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V50" s="21" t="inlineStr">
+        <is>
+          <t>MRC website</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21.75" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-046</t>
+          <t>MFL-2026-052</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Climate data</t>
+          <t>LULC classification</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Water / hydrology</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>CIV-NZ — N'Zi Watershed</t>
+          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>Climate station observations</t>
+          <t>basin and country levels</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>since 2014</t>
+          <t>present</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>AfricaRice</t>
+          <t>IWMI</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
+          <t>s.douangsavanh@cgiar.org</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Restricted — contact data owner</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
@@ -6941,83 +7147,85 @@
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Climate data from climate stations for three major cities in the watershed (coverage period varies depending on the station); climate data from M'Be research station </t>
+          <t>MRC produced the data</t>
         </is>
       </c>
       <c r="S51" s="5" t="n"/>
-      <c r="T51" s="4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monthly </t>
-        </is>
-      </c>
-      <c r="V51" s="4" t="inlineStr">
-        <is>
-          <t>NHMS for the synoptic climate stations</t>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="U51" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V51" s="10" t="inlineStr">
+        <is>
+          <t>MRC website</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21.75" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-067</t>
+          <t>MFL-2026-053</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Climate data</t>
+          <t>Sekong River Basin Management Plan</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Water / hydrology</t>
+          <t>Socio-economic / livelihoods</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>CIV-NZ — N'Zi Watershed</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Tabular</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>0.05° × 0.05° and 0.1° x 0.1°, depending on the products</t>
+          <t>report-country and basin level</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>1979 - present</t>
+          <t>2021-2025</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>AfricaRice</t>
+          <t>IWMI</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
+          <t>s.douangsavanh@cgiar.org</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Restricted — contact data owner</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
@@ -7035,81 +7243,85 @@
       <c r="Q52" s="4" t="n"/>
       <c r="R52" s="4" t="inlineStr">
         <is>
-          <t>Gridded daily climate data from CHIRPS and ERA5 climate reanalysis</t>
+          <t>Ministry of Agriculture and Environment (MOAE), Lao PDR</t>
         </is>
       </c>
       <c r="S52" s="5" t="n"/>
-      <c r="T52" s="4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seasonal </t>
-        </is>
-      </c>
-      <c r="V52" s="4" t="inlineStr">
-        <is>
-          <t>CHIRPS data ( https://doi.org/10.15780/G2JQ0P). ERA5 AgERA5 v2.0 (https://doi.org/10.24381/f9c1f09d)</t>
+      <c r="T52" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U52" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V52" s="21" t="inlineStr">
+        <is>
+          <t>website-MOAE</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21.75" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-048</t>
+          <t>MFL-2026-054</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Soil dataset</t>
+          <t>soil classification</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Land cover / land use</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>GLOBAL — Global / cross-landscape</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Soil dataset</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>5-min resolution</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>2015</v>
+          <t>basin and country levels</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>present</t>
+        </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>AfricaRice</t>
+          <t>IWMI</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
+          <t>s.douangsavanh@cgiar.org</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Restricted — contact data owner</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -7127,83 +7339,85 @@
       <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="inlineStr">
         <is>
-          <t>High-resolution soil profile database for crop modeling applications. Files are '*.SOL' file format (DSSAT soil database) for each country worldwide.</t>
+          <t>Ministry of Agriculture and Environment (MOAE), Lao PDR</t>
         </is>
       </c>
       <c r="S53" s="5" t="n"/>
-      <c r="T53" s="4" t="n">
-        <v>2015</v>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="V53" s="4" t="inlineStr">
-        <is>
-          <t>International Research Institute for Climate and Society (IRI); Michigan State University (MSU); HarvestChoice, International Food Policy Research Institute (IFPRI), 2015, "Global High-Resolution Soil Profile Database for Crop Modeling Applications", https://doi.org/10.7910/DVN/1PEEY0</t>
+      <c r="T53" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U53" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V53" s="10" t="inlineStr">
+        <is>
+          <t>website-MOAE</t>
         </is>
       </c>
     </row>
     <row r="54" ht="21.75" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-066</t>
+          <t>MFL-2026-055</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Soil dataset</t>
+          <t>Crop fields (2025) - focus on NUS crops</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Degradation / land health</t>
+          <t>Agrobiodiversity / crops</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>GLOBAL — Global / cross-landscape</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Soil dataset</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>250 m</t>
+          <t>Pucallpa Aguaytia Corridor (Andean Amazon Landscape)</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>AfricaRice</t>
+          <t>CIP</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
+          <t>javier.ochoa@cgiar.org</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>Restricted — contact data owner</t>
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
@@ -7214,55 +7428,57 @@
       <c r="N54" s="4" t="n"/>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>server and drive</t>
+          <t>CIP Dataverse</t>
         </is>
       </c>
       <c r="P54" s="4" t="n"/>
       <c r="Q54" s="4" t="n"/>
       <c r="R54" s="4" t="inlineStr">
         <is>
-          <t>Soil data from SoilGrids</t>
+          <t>Amazonian tubers classified as Neglected and Underutilized Crop Species (NUS crops) in each farmers field, accurately documenting the characteristics of these species in situ. This process generated a comprehensive dataset comprising seven different crops: cassava (Manihot esculenta), sweet potato (Ipomoea batatas), aerial potato (Dioscorea bulbifera L.), achipa or chuin (Pachyrhizus tuberosus), pituca (Colocasia spp., Xanthosoma spp.), dale-dale (Calathea allouia), and sacha papa (Dioscorea bulbifera). Overall, the study captured the main characteristics of 683 varieties/404 species recorded across 273 mapped plots from 221 farmer households. The dataset is organized into: A) Household information, B) Field information and land-use history, C) Species names, D) Variety names, and E) Community collection points of NUS crops</t>
         </is>
       </c>
       <c r="S54" s="5" t="n"/>
-      <c r="T54" s="4" t="n">
-        <v>2026</v>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
+      <c r="T54" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U54" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V54" s="14" t="inlineStr">
-        <is>
-          <t>SoilGrids - Global gridded soil information (https://soilgrids.org/)</t>
+      <c r="V54" s="21" t="inlineStr">
+        <is>
+          <t>https://data.cipotato.org/</t>
         </is>
       </c>
     </row>
     <row r="55" ht="21.75" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-050</t>
+          <t>MFL-2026-056</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>watershed boundary</t>
+          <t>Crop fields (2023)  focus on 	Potatoes, Oca, Mashua and andean fruit trees</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Boundaries / admin units</t>
+          <t>Agrobiodiversity / crops</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -7272,27 +7488,27 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>basin and country levels</t>
+          <t>Cumbal (Andean Amazon Landscape)</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>IWMI</t>
-        </is>
-      </c>
-      <c r="J55" s="23" t="inlineStr">
-        <is>
-          <t>s.douangsavanh@cgiar.org</t>
+          <t>CIP</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>javier.ochoa@cgiar.org</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>CGIAR-internal</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -7308,61 +7524,57 @@
       <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>server and drive</t>
+          <t>CIP Dataverse</t>
         </is>
       </c>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="inlineStr">
         <is>
-          <t>MRC produced the data</t>
-        </is>
-      </c>
-      <c r="S55" s="4" t="inlineStr">
-        <is>
-          <t>MRC produced the data</t>
-        </is>
-      </c>
+          <t>A total of 206 farmers in Cumbal, Colombia, were surveyed utilizing ArcGIS Survey 123. Each farmer's field was physically visited, and the 'Participatory Mapping of Farmers' Fields' tool was employed to delineate polygons for each 'shagra', accurately determining their respective areas. This process captured the characteristics of 557 mapped plots across 206 farmers' households. The resultant comprehensive dataset comprises five distinct databases: A) Preliminary Information, B) Shagra Information, C) Land Use Over the Years, and D) Variety Names. These datasets have been individualized and standardized using the common identifiers 'GlobalID Household' and 'GlobalID Shagra'.</t>
+        </is>
+      </c>
+      <c r="S55" s="5" t="n"/>
       <c r="T55" s="4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="U55" s="8" t="inlineStr">
+      <c r="U55" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>MRC website</t>
+      <c r="V55" s="10" t="inlineStr">
+        <is>
+          <t>https://data.cipotato.org/</t>
         </is>
       </c>
     </row>
     <row r="56" ht="21.75" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-051</t>
+          <t>MFL-2026-057</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>river network</t>
+          <t>Crop fields (2023)  focus on Banana, Pumpkins, Taro, Mustard</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Water / hydrology</t>
+          <t>Agrobiodiversity / crops</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -7372,27 +7584,27 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>basin and country levels</t>
+          <t>Son La  and Lao Cai (Vietnam)</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>IWMI</t>
-        </is>
-      </c>
-      <c r="J56" s="23" t="inlineStr">
-        <is>
-          <t>s.douangsavanh@cgiar.org</t>
+          <t>CIP</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>javier.ochoa@cgiar.org</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>CGIAR-internal</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -7408,51 +7620,47 @@
       <c r="N56" s="4" t="n"/>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>server and drive</t>
+          <t>CIP Dataverse</t>
         </is>
       </c>
       <c r="P56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
       <c r="R56" s="4" t="inlineStr">
         <is>
-          <t>MRC produced the data</t>
-        </is>
-      </c>
-      <c r="S56" s="4" t="inlineStr">
-        <is>
-          <t>MRC produced the data</t>
-        </is>
-      </c>
+          <t>A total of 200 farmers in Vietnam, were surveyed utilizing ArcGIS Survey 123. Each farmer's field was physically visited, and the 'Participatory Mapping of Farmers' Fields' tool was employed to delineate polygons for each 'parcel', accurately determining their respective areas. This process captured the characteristics of 773 mapped plots across 200 farmers' households. The resultant comprehensive dataset comprises five distinct databases: A) Preliminary Information, B) Plot Information, C) Plot and Land Use, D) Crop Information, E) Variety Names. These datasets have been individualized and standardized using the common identifiers 'GlobalID Household' and 'GlobalID Plot'.</t>
+        </is>
+      </c>
+      <c r="S56" s="5" t="n"/>
       <c r="T56" s="4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
+      <c r="U56" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>MRC website</t>
+      <c r="V56" s="21" t="inlineStr">
+        <is>
+          <t>https://data.cipotato.org/</t>
         </is>
       </c>
     </row>
     <row r="57" ht="21.75" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-052</t>
+          <t>MFL-2026-058</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>LULC classification</t>
+          <t>Forest cover in Cambodia (2015-2023)</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -7467,37 +7675,37 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>basin and country levels</t>
+          <t>30m</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>2015-2023</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>IWMI</t>
-        </is>
-      </c>
-      <c r="J57" s="23" t="inlineStr">
-        <is>
-          <t>s.douangsavanh@cgiar.org</t>
+          <t>WorldFish</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>CGIAR-internal</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>Restricted — contact data owner</t>
+          <t>Other (specify in notes)</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
@@ -7508,45 +7716,47 @@
       <c r="N57" s="4" t="n"/>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>server and drive</t>
+          <t>local drive</t>
         </is>
       </c>
       <c r="P57" s="4" t="n"/>
       <c r="Q57" s="4" t="n"/>
       <c r="R57" s="4" t="inlineStr">
         <is>
-          <t>MRC produced the data</t>
+          <t>Cambodia's annual forest cover developed through the USAID's Cambodia Supporting Forests and Biodiversity (USAID SFB) project</t>
         </is>
       </c>
       <c r="S57" s="5" t="n"/>
-      <c r="T57" s="4" t="n">
-        <v>2020</v>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U57" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>MRC website</t>
+      <c r="V57" s="10" t="inlineStr">
+        <is>
+          <t>https://data.opendevelopmentmekong.net/map/forest-cove-2015-present</t>
         </is>
       </c>
     </row>
     <row r="58" ht="21.75" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-053</t>
+          <t>MFL-2026-059</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Sekong River Basin Management Plan</t>
+          <t>Community fisheries</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -7556,42 +7766,42 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>NATIONAL — Country-wide coverage</t>
+          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>Vector</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>report-country and basin level</t>
+          <t>village level</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>2021-2025</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>IWMI</t>
-        </is>
-      </c>
-      <c r="J58" s="23" t="inlineStr">
-        <is>
-          <t>s.douangsavanh@cgiar.org</t>
+          <t>WorldFish</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>CGIAR-internal</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>Restricted — contact data owner</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
@@ -7602,14 +7812,14 @@
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>server and drive</t>
+          <t>local drive</t>
         </is>
       </c>
       <c r="P58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
       <c r="R58" s="4" t="inlineStr">
         <is>
-          <t>Ministry of Agriculture and Environment (MOAE), Lao PDR</t>
+          <t>provides geographic boundaries, size and the number of villages covered by each community fishery</t>
         </is>
       </c>
       <c r="S58" s="5" t="n"/>
@@ -7618,41 +7828,41 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
+      <c r="U58" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>website-MOAE</t>
+      <c r="V58" s="21" t="inlineStr">
+        <is>
+          <t>https://data.opendevelopmentcambodia.net/en/dataset/community-fisheries-map-for-cambodia-2011</t>
         </is>
       </c>
     </row>
     <row r="59" ht="21.75" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-054</t>
+          <t>MFL-2026-060</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>soil classification</t>
+          <t>Marine fisheries management area</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Biodiversity / ecosystems</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>NATIONAL — Country-wide coverage</t>
+          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -7662,32 +7872,32 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>basin and country levels</t>
+          <t>boundary level</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>present</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>IWMI</t>
-        </is>
-      </c>
-      <c r="J59" s="23" t="inlineStr">
-        <is>
-          <t>s.douangsavanh@cgiar.org</t>
+          <t>WorldFish</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>CGIAR-internal</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>Restricted — contact data owner</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
@@ -7698,14 +7908,14 @@
       <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>server and drive</t>
+          <t>local drive</t>
         </is>
       </c>
       <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
       <c r="R59" s="4" t="inlineStr">
         <is>
-          <t>Ministry of Agriculture and Environment (MOAE), Lao PDR</t>
+          <t>Marine fisheries management area to enhance the protection of the marine biodiversity and fisheries livelihood within​ Archipelago in marine areas, divided into 6 classifications such as community fisheries, conservation areas, fisheries refugias, multiple use areas, protected area, and recreational areas.</t>
         </is>
       </c>
       <c r="S59" s="5" t="n"/>
@@ -7714,41 +7924,41 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="U59" s="8" t="inlineStr">
+      <c r="U59" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>website-MOAE</t>
+      <c r="V59" s="10" t="inlineStr">
+        <is>
+          <t>https://data.opendevelopmentcambodia.net/en/dataset/marine-fisheries-management-area</t>
         </is>
       </c>
     </row>
     <row r="60" ht="21.75" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-055</t>
+          <t>MFL-2026-061</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Crop fields (2025) - focus on NUS crops</t>
+          <t>Fish dependency</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Agrobiodiversity / crops</t>
+          <t>Socio-economic / livelihoods</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>NATIONAL — Country-wide coverage</t>
+          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -7758,30 +7968,32 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Pucallpa Aguaytia Corridor (Andean Amazon Landscape)</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>2025</v>
+          <t>commune level (admin-level-3)</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>CIP</t>
-        </is>
-      </c>
-      <c r="J60" s="23" t="inlineStr">
-        <is>
-          <t>javier.ochoa@cgiar.org</t>
+          <t>WorldFish</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>CGIAR-internal</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>Restricted — contact data owner</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
@@ -7792,14 +8004,14 @@
       <c r="N60" s="4" t="n"/>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>CIP Dataverse</t>
+          <t>local drive</t>
         </is>
       </c>
       <c r="P60" s="4" t="n"/>
       <c r="Q60" s="4" t="n"/>
       <c r="R60" s="4" t="inlineStr">
         <is>
-          <t>Amazonian tubers classified as Neglected and Underutilized Crop Species (NUS crops) in each farmers field, accurately documenting the characteristics of these species in situ. This process generated a comprehensive dataset comprising seven different crops: cassava (Manihot esculenta), sweet potato (Ipomoea batatas), aerial potato (Dioscorea bulbifera L.), achipa or chuin (Pachyrhizus tuberosus), pituca (Colocasia spp., Xanthosoma spp.), dale-dale (Calathea allouia), and sacha papa (Dioscorea bulbifera). Overall, the study captured the main characteristics of 683 varieties/404 species recorded across 273 mapped plots from 221 farmer households. The dataset is organized into: A) Household information, B) Field information and land-use history, C) Species names, D) Variety names, and E) Community collection points of NUS crops</t>
+          <t>Fsh dependency rate based on the communal statistics</t>
         </is>
       </c>
       <c r="S60" s="5" t="n"/>
@@ -7808,31 +8020,31 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr">
+      <c r="U60" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V60" s="15" t="inlineStr">
-        <is>
-          <t>https://data.cipotato.org/</t>
+      <c r="V60" s="21" t="inlineStr">
+        <is>
+          <t>https://data.opendevelopmentcambodia.net/en/dataset/map_fish_dependency</t>
         </is>
       </c>
     </row>
     <row r="61" ht="21.75" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-056</t>
+          <t>MFL-2026-062</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Crop fields (2023)  focus on 	Potatoes, Oca, Mashua and andean fruit trees</t>
+          <t>Rice ecosystem</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -7842,7 +8054,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>NATIONAL — Country-wide coverage</t>
+          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -7852,30 +8064,32 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Cumbal (Andean Amazon Landscape)</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>2023</v>
+          <t>boundary level</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>CIP</t>
-        </is>
-      </c>
-      <c r="J61" s="23" t="inlineStr">
-        <is>
-          <t>javier.ochoa@cgiar.org</t>
+          <t>WorldFish</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>CGIAR-internal</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>Restricted — contact data owner</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
@@ -7886,14 +8100,14 @@
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>CIP Dataverse</t>
+          <t>local drive</t>
         </is>
       </c>
       <c r="P61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="inlineStr">
         <is>
-          <t>A total of 206 farmers in Cumbal, Colombia, were surveyed utilizing ArcGIS Survey 123. Each farmer's field was physically visited, and the 'Participatory Mapping of Farmers' Fields' tool was employed to delineate polygons for each 'shagra', accurately determining their respective areas. This process captured the characteristics of 557 mapped plots across 206 farmers' households. The resultant comprehensive dataset comprises five distinct databases: A) Preliminary Information, B) Shagra Information, C) Land Use Over the Years, and D) Variety Names. These datasets have been individualized and standardized using the common identifiers 'GlobalID Household' and 'GlobalID Shagra'.</t>
+          <t>locations of rice in 4 categories: Rainfed upland rice, Recession rice, Deep water/floating rice, Rainfed lowland rice</t>
         </is>
       </c>
       <c r="S61" s="5" t="n"/>
@@ -7902,135 +8116,137 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
+      <c r="U61" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V61" s="15" t="inlineStr">
-        <is>
-          <t>https://data.cipotato.org/</t>
+      <c r="V61" s="10" t="inlineStr">
+        <is>
+          <t>https://data.opendevelopmentcambodia.net/en/dataset/map-rice-ecosystem</t>
         </is>
       </c>
     </row>
     <row r="62" ht="21.75" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-057</t>
+          <t>MFL-2026-063</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Crop fields (2023)  focus on Banana, Pumpkins, Taro, Mustard</t>
+          <t>India's open natural ecosystem</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Agrobiodiversity / crops</t>
+          <t>Ecosystem condition</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>NATIONAL — Country-wide coverage</t>
+          <t>IND-CH — Central India Highlands</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>Son La  and Lao Cai (Vietnam)</t>
-        </is>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>2023</v>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>2018-2024</t>
+        </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>CIP</t>
-        </is>
-      </c>
-      <c r="J62" s="23" t="inlineStr">
-        <is>
-          <t>javier.ochoa@cgiar.org</t>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Smitha Krishnan (s.krishnan@cgiar.org)</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>CGIAR-internal</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>Restricted — contact data owner</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Processed</t>
         </is>
       </c>
       <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>CIP Dataverse</t>
+          <t>ATREE -Server - GEE</t>
         </is>
       </c>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="n"/>
       <c r="R62" s="4" t="inlineStr">
         <is>
-          <t>A total of 200 farmers in Vietnam, were surveyed utilizing ArcGIS Survey 123. Each farmer's field was physically visited, and the 'Participatory Mapping of Farmers' Fields' tool was employed to delineate polygons for each 'parcel', accurately determining their respective areas. This process captured the characteristics of 773 mapped plots across 200 farmers' households. The resultant comprehensive dataset comprises five distinct databases: A) Preliminary Information, B) Plot Information, C) Plot and Land Use, D) Crop Information, E) Variety Names. These datasets have been individualized and standardized using the common identifiers 'GlobalID Household' and 'GlobalID Plot'.</t>
+          <t>India's Open Natural Ecosystems at a 10-m scale,</t>
         </is>
       </c>
       <c r="S62" s="5" t="n"/>
       <c r="T62" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="V62" s="15" t="inlineStr">
-        <is>
-          <t>https://data.cipotato.org/</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U62" s="11" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V62" s="21" t="inlineStr">
+        <is>
+          <t>open-natural-ecosystems</t>
         </is>
       </c>
     </row>
     <row r="63" ht="21.75" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-058</t>
+          <t>MFL-2026-064</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Forest cover in Cambodia (2015-2023)</t>
+          <t>Tree conservation and restoration priority areas</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Land cover / land use</t>
+          <t>Decision-support outputs</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -8040,22 +8256,22 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>30m</t>
+          <t>1000m</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>2015-2023</t>
+          <t>2017-2025</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>WorldFish</t>
+          <t>Alliance Bioversity-CIAT</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
+          <t>Hannes Gaisberger, h.gaisberger@cgiar.org</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -8065,7 +8281,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>CGIAR Open Access</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
@@ -8076,80 +8292,87 @@
       <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>local drive</t>
+          <t>Dataverse repository</t>
         </is>
       </c>
       <c r="P63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
       <c r="R63" s="4" t="inlineStr">
         <is>
-          <t>Cambodia's annual forest cover developed through the USAID's Cambodia Supporting Forests and Biodiversity (USAID SFB) project</t>
+          <t>Conservation for Restoration (C4R) tool KENYA: mapping the vulnerability and priority areas for conservation and restoration of 78 native tree species. Linked to D4R</t>
         </is>
       </c>
       <c r="S63" s="5" t="n"/>
       <c r="T63" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="V63" s="30" t="inlineStr">
-        <is>
-          <t>https://data.opendevelopmentmekong.net/map/forest-cove-2015-present</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U63" s="11" t="inlineStr">
+        <is>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V63" s="10" t="inlineStr">
+        <is>
+          <t>https://dataverse.harvard.edu/citation?persistentId=doi:10.7910/DVN/2ZQTB2</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>220 MB</t>
         </is>
       </c>
     </row>
     <row r="64" ht="21.75" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-059</t>
+          <t>MFL-2026-065</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Community fisheries</t>
+          <t>Soil health status and texture</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Socio-economic / livelihoods</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
+          <t>ZWE-MB — Mbire – Lower Zambezi Valley</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>village level</t>
-        </is>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>2011</v>
+          <t>Ward level</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>WorldFish</t>
+          <t>CIMMYT</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
+          <t>Telma.SIBANDA@um6p.ma</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
@@ -8159,91 +8382,89 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
+          <t>CGIAR Open Access</t>
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>Validated</t>
+          <t>Processed</t>
         </is>
       </c>
       <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>local drive</t>
+          <t>Drive</t>
         </is>
       </c>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
       <c r="R64" s="4" t="inlineStr">
         <is>
-          <t>provides geographic boundaries, size and the number of villages covered by each community fishery</t>
+          <t>Ward-level soil texture, nitrogen, and carbon content data — Original landscape entry: Mbire: Wards 2 and 3</t>
         </is>
       </c>
       <c r="S64" s="5" t="n"/>
       <c r="T64" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="V64" s="30" t="inlineStr">
-        <is>
-          <t>https://data.opendevelopmentcambodia.net/en/dataset/community-fisheries-map-for-cambodia-2011</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U64" s="11" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V64" s="21" t="inlineStr">
+        <is>
+          <t>Internal Available on request</t>
         </is>
       </c>
     </row>
     <row r="65" ht="21.75" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-060</t>
+          <t>MFL-2026-066</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Marine fisheries management area</t>
+          <t>SoilGrids gridded soil information</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Biodiversity / ecosystems</t>
+          <t>Degradation / land health</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Vector</t>
-        </is>
-      </c>
+          <t>GLOBAL — Global / cross-landscape</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>boundary level</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="n">
-        <v>2018</v>
+          <t>250 m</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>WorldFish</t>
+          <t>AfricaRice</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
+          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -8264,80 +8485,82 @@
       <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>local drive</t>
+          <t>server and drive</t>
         </is>
       </c>
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Marine fisheries management area to enhance the protection of the marine biodiversity and fisheries livelihood within​ Archipelago in marine areas, divided into 6 classifications such as community fisheries, conservation areas, fisheries refugias, multiple use areas, protected area, and recreational areas.</t>
+          <t>Soil data from SoilGrids</t>
         </is>
       </c>
       <c r="S65" s="5" t="n"/>
       <c r="T65" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="inlineStr">
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U65" s="11" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="V65" s="30" t="inlineStr">
-        <is>
-          <t>https://data.opendevelopmentcambodia.net/en/dataset/marine-fisheries-management-area</t>
+      <c r="V65" s="10" t="inlineStr">
+        <is>
+          <t>SoilGrids - Global gridded soil information (https://soilgrids.org/)</t>
         </is>
       </c>
     </row>
     <row r="66" ht="21.75" customHeight="1">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-061</t>
+          <t>MFL-2026-067</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Fish dependency</t>
+          <t>Gridded climate data (CHIRPS and AgERA5)</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Socio-economic / livelihoods</t>
+          <t>Water / hydrology</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
+          <t>CIV-NZ — N'Zi Watershed</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Tabular</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>commune level (admin-level-3)</t>
-        </is>
-      </c>
-      <c r="H66" s="4" t="n">
-        <v>2015</v>
+          <t>0.05° × 0.05° and 0.1° x 0.1°, depending on the products</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>1979 - present</t>
+        </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>WorldFish</t>
+          <t>AfricaRice</t>
         </is>
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
+          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr">
@@ -8358,80 +8581,82 @@
       <c r="N66" s="4" t="n"/>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>local drive</t>
+          <t>server and drive</t>
         </is>
       </c>
       <c r="P66" s="4" t="n"/>
       <c r="Q66" s="4" t="n"/>
       <c r="R66" s="4" t="inlineStr">
         <is>
-          <t>Fsh dependency rate based on the communal statistics</t>
+          <t>Gridded daily climate data from CHIRPS and ERA5 climate reanalysis</t>
         </is>
       </c>
       <c r="S66" s="5" t="n"/>
       <c r="T66" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="U66" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="V66" s="30" t="inlineStr">
-        <is>
-          <t>https://data.opendevelopmentcambodia.net/en/dataset/map_fish_dependency</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U66" s="11" t="inlineStr">
+        <is>
+          <t>Seasonal</t>
+        </is>
+      </c>
+      <c r="V66" s="21" t="inlineStr">
+        <is>
+          <t>CHIRPS data ( https://doi.org/10.15780/G2JQ0P). ERA5 AgERA5 v2.0 (https://doi.org/10.24381/f9c1f09d)</t>
         </is>
       </c>
     </row>
     <row r="67" ht="21.75" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-062</t>
+          <t>MFL-2026-068</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rice ecosystem </t>
+          <t>Tree conservation and restoration priority areas</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Agrobiodiversity / crops</t>
+          <t>Decision-support outputs</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>MEK-3S — 3S Basins (Sekong, Sesan, Srepok)</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Vector</t>
+          <t>Raster</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>boundary level</t>
-        </is>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>2015</v>
+          <t>1000m</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>2017-2025</t>
+        </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>WorldFish</t>
+          <t>Alliance Bioversity-CIAT</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>Shwu Jiau Teoh (s.teoh@cgiar.org)</t>
+          <t>Hannes Gaisberger, h.gaisberger@cgiar.org</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
@@ -8441,68 +8666,65 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-      <c r="M67" s="4" t="inlineStr">
-        <is>
-          <t>Validated</t>
-        </is>
-      </c>
+          <t>CGIAR Open Access</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="n"/>
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>local drive</t>
+          <t>One drive</t>
         </is>
       </c>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="n"/>
       <c r="R67" s="4" t="inlineStr">
         <is>
-          <t>locations of rice in 4 categories: Rainfed upland rice, Recession rice, Deep water/floating rice, Rainfed lowland rice</t>
+          <t>Conservation for Restoration (C4R) tool LAOS: mapping the vulnerability and priority areas for conservation and restoration of 79 native tree species. Linked to D4R</t>
         </is>
       </c>
       <c r="S67" s="5" t="n"/>
       <c r="T67" s="4" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="U67" s="8" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="V67" s="30" t="inlineStr">
-        <is>
-          <t>https://data.opendevelopmentcambodia.net/en/dataset/map-rice-ecosystem</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U67" s="11" t="inlineStr">
+        <is>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V67" s="10" t="n"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>250 MB</t>
         </is>
       </c>
     </row>
     <row r="68" ht="21.75" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MFL-2026-063</t>
+          <t>MFL-2026-069</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>India's open natural ecosystem</t>
+          <t>Tree conservation and restoration priority areas</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Ecosystem condition</t>
+          <t>Decision-support outputs</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>IND-CH — Central India Highlands</t>
+          <t>NATIONAL — Country-wide coverage</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -8512,12 +8734,12 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>10m</t>
+          <t>1000m</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>2018-2024</t>
+          <t>2017-2025</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -8527,7 +8749,7 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>Smitha Krishnan (s.krishnan@cgiar.org)</t>
+          <t>Hannes Gaisberger, h.gaisberger@cgiar.org</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr">
@@ -8537,327 +8759,1318 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>CC BY 4.0</t>
-        </is>
-      </c>
-      <c r="M68" s="4" t="inlineStr">
-        <is>
-          <t>Processed</t>
-        </is>
-      </c>
+          <t>CGIAR Open Access</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="n"/>
       <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>ATREE -Server - GEE</t>
+          <t>One drive</t>
         </is>
       </c>
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="inlineStr">
         <is>
-          <t>India's Open Natural Ecosystems at a 10-m scale,</t>
+          <t>Conservation for Restoration (C4R) tool VIETNAM: mapping the vulnerability and priority areas for conservation and restoration of 66 native tree species. Linked to D4R</t>
         </is>
       </c>
       <c r="S68" s="5" t="n"/>
-      <c r="T68" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="U68" s="8" t="inlineStr">
-        <is>
-          <t>Static</t>
-        </is>
-      </c>
-      <c r="V68" s="30" t="inlineStr">
-        <is>
-          <t>open-natural-ecosystems</t>
+      <c r="T68" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U68" s="11" t="inlineStr">
+        <is>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V68" s="21" t="n"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>250 MB</t>
         </is>
       </c>
     </row>
     <row r="69" ht="21.75" customHeight="1">
-      <c r="A69" s="3" t="n"/>
-      <c r="B69" s="4" t="n"/>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="n"/>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="n"/>
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-070</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Coding Matrix: Ecosystem Services in Tropical Cattle Systems — A Systematic Literature Review across Five Thematic Streams</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Ecosystem services</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>GLOBAL — Global / cross-landscape</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Tabular</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="n"/>
-      <c r="J69" s="4" t="n"/>
-      <c r="K69" s="4" t="n"/>
-      <c r="L69" s="4" t="n"/>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>Stefan Burkart (s.burkart@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>CC BY 4.0</t>
+        </is>
+      </c>
       <c r="M69" s="4" t="n"/>
-      <c r="N69" s="4" t="n"/>
-      <c r="O69" s="4" t="n"/>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>.xlsx</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>Harvard Dataverse</t>
+        </is>
+      </c>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="n"/>
-      <c r="R69" s="4" t="n"/>
-      <c r="S69" s="5" t="n"/>
-      <c r="T69" s="4" t="n"/>
+      <c r="R69" s="4" t="inlineStr">
+        <is>
+          <t>Workbook documenting ~549 coded study entries from a systematic literature review on ecosystem services in tropical and subtropical cattle systems, coded consistently across five thematic streams for cross-paper comparison and filtering. Studies may appear in multiple streams.</t>
+        </is>
+      </c>
+      <c r="S69" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="T69" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U69" s="11" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V69" s="10" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/XD96CL</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>586 KB</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="21.75" customHeight="1">
-      <c r="A70" s="3" t="n"/>
-      <c r="B70" s="4" t="n"/>
-      <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="n"/>
-      <c r="F70" s="4" t="n"/>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-071</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Urochloa hybrid adoption in Latin America and the Caribbean 2001-2024: An analysis of the land use, social, economic, and environmental impacts in 27 countries</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Latin America and the Caribbean</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>Agrobiodiversity / crops</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>GLOBAL — Global / cross-landscape</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Tabular</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="n"/>
-      <c r="J70" s="4" t="n"/>
-      <c r="K70" s="4" t="n"/>
-      <c r="L70" s="4" t="n"/>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>2001-2024</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>Stefan Burkart (s.burkart@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>CC0 1.0</t>
+        </is>
+      </c>
       <c r="M70" s="4" t="n"/>
-      <c r="N70" s="4" t="n"/>
-      <c r="O70" s="4" t="n"/>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>1_hybrid_calculation_determinist_LAC.xlsx; 2_environmental calculation_determinist_LAC.xlsx</t>
+        </is>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>Harvard Dataverse</t>
+        </is>
+      </c>
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
-      <c r="R70" s="4" t="n"/>
-      <c r="S70" s="5" t="n"/>
-      <c r="T70" s="4" t="n"/>
+      <c r="R70" s="4" t="inlineStr">
+        <is>
+          <t>Analysis of interspecific Urochloa forage-grass hybrid adoption across 27 Latin American and Caribbean countries, 2001-2024. Estimates over 1.09 million adopting farmers on 1.62 million cumulative hectares, projects cumulative forage value of US$47-62 billion by 2033, and estimates potential greenhouse gas emission reductions of 16.9-56.3 Mt CO2-eq by that timeframe.</t>
+        </is>
+      </c>
+      <c r="S70" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="T70" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U70" s="11" t="inlineStr">
+        <is>
+          <t>Static</t>
+        </is>
+      </c>
+      <c r="V70" s="21" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.7910/DVN/L86VZ9</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>104.2 KB (2 files)</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="21.75" customHeight="1">
-      <c r="A71" s="3" t="n"/>
-      <c r="B71" s="4" t="n"/>
-      <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
-      <c r="J71" s="4" t="n"/>
-      <c r="K71" s="4" t="n"/>
-      <c r="L71" s="4" t="n"/>
-      <c r="M71" s="4" t="n"/>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-072</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Provinces and Districts</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>Admin level 2 and 3</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Current boundaries</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>Other (specify in notes)</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
       <c r="N71" s="4" t="n"/>
-      <c r="O71" s="4" t="n"/>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>One Drive</t>
+        </is>
+      </c>
       <c r="P71" s="4" t="n"/>
       <c r="Q71" s="4" t="n"/>
-      <c r="R71" s="4" t="n"/>
-      <c r="S71" s="5" t="n"/>
-      <c r="T71" s="4" t="n"/>
+      <c r="R71" s="4" t="inlineStr">
+        <is>
+          <t>Administrative boundaries for Ucayali, Peru</t>
+        </is>
+      </c>
+      <c r="S71" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T71" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U71" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V71" s="10" t="inlineStr">
+        <is>
+          <t>https://www.datosabiertos.gob.pe/dataset/limites-departamentales</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="21.75" customHeight="1">
-      <c r="A72" s="3" t="n"/>
-      <c r="B72" s="4" t="n"/>
-      <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="n"/>
-      <c r="F72" s="4" t="n"/>
-      <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="n"/>
-      <c r="J72" s="4" t="n"/>
-      <c r="K72" s="4" t="n"/>
-      <c r="L72" s="4" t="n"/>
-      <c r="M72" s="4" t="n"/>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-073</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>National Protected Natural Areas</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>Boundary level</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>Other (specify in notes)</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
       <c r="N72" s="4" t="n"/>
-      <c r="O72" s="4" t="n"/>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>One Drive</t>
+        </is>
+      </c>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
-      <c r="R72" s="4" t="n"/>
-      <c r="S72" s="5" t="n"/>
-      <c r="T72" s="4" t="n"/>
+      <c r="R72" s="4" t="inlineStr">
+        <is>
+          <t>National Protected Natural Areas clipped to  Ucayali</t>
+        </is>
+      </c>
+      <c r="S72" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T72" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U72" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V72" s="21" t="inlineStr">
+        <is>
+          <t>https://geo.sernanp.gob.pe/visorsernanp/</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="21.75" customHeight="1">
-      <c r="A73" s="3" t="n"/>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-074</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Regional Conservation Areas</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>Boundary level</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>Other (specify in notes)</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
       <c r="N73" s="4" t="n"/>
-      <c r="O73" s="4" t="n"/>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>One Drive</t>
+        </is>
+      </c>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
-      <c r="R73" s="4" t="n"/>
-      <c r="S73" s="5" t="n"/>
-      <c r="T73" s="4" t="n"/>
+      <c r="R73" s="4" t="inlineStr">
+        <is>
+          <t>Regional Conservation Areas clipped to Ucayali</t>
+        </is>
+      </c>
+      <c r="S73" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T73" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U73" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V73" s="10" t="inlineStr">
+        <is>
+          <t>https://geo.sernanp.gob.pe/visorsernanp/</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="21.75" customHeight="1">
-      <c r="A74" s="3" t="n"/>
-      <c r="B74" s="4" t="n"/>
-      <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="n"/>
-      <c r="F74" s="4" t="n"/>
-      <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="n"/>
-      <c r="J74" s="4" t="n"/>
-      <c r="K74" s="4" t="n"/>
-      <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="n"/>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-075</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Indigenous Territories</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>Boundaries / admin units</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>Boundary level</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>Other (specify in notes)</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
       <c r="N74" s="4" t="n"/>
-      <c r="O74" s="4" t="n"/>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>One Drive</t>
+        </is>
+      </c>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
-      <c r="R74" s="4" t="n"/>
-      <c r="S74" s="5" t="n"/>
-      <c r="T74" s="4" t="n"/>
+      <c r="R74" s="4" t="inlineStr">
+        <is>
+          <t>Indigenous Territories clipped to Ucayali</t>
+        </is>
+      </c>
+      <c r="S74" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T74" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U74" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V74" s="21" t="inlineStr">
+        <is>
+          <t>https://www.raisg.org/es/mapas/</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="21.75" customHeight="1">
-      <c r="A75" s="3" t="n"/>
-      <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4" t="n"/>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="n"/>
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-076</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>National Ecosystem Map</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Biodiversity / ecosystems</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="n"/>
-      <c r="J75" s="4" t="n"/>
-      <c r="K75" s="4" t="n"/>
-      <c r="L75" s="4" t="n"/>
-      <c r="M75" s="4" t="n"/>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>Other (specify in notes)</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
       <c r="N75" s="4" t="n"/>
-      <c r="O75" s="4" t="n"/>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>One Drive</t>
+        </is>
+      </c>
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
-      <c r="R75" s="4" t="n"/>
-      <c r="S75" s="5" t="n"/>
-      <c r="T75" s="4" t="n"/>
+      <c r="R75" s="4" t="inlineStr">
+        <is>
+          <t>Spatial distribution and classification of ecosystem within Ucayali department, derived from Peru´s National Ecosystem Map 2018, and aggregated by adminstrative provinces and districts level</t>
+        </is>
+      </c>
+      <c r="S75" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T75" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U75" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V75" s="10" t="inlineStr">
+        <is>
+          <t>https://geoservidor.minam.gob.pe/recursos/intercambio-de-datos/</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="21.75" customHeight="1">
-      <c r="A76" s="3" t="n"/>
-      <c r="B76" s="4" t="n"/>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="n"/>
-      <c r="F76" s="4" t="n"/>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-077</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Human Footprint map</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>Pressures / drivers</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
       <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="n"/>
-      <c r="J76" s="4" t="n"/>
-      <c r="K76" s="4" t="n"/>
-      <c r="L76" s="4" t="n"/>
-      <c r="M76" s="4" t="n"/>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>2012, 2015, 2018, 2021</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>Other (specify in notes)</t>
+        </is>
+      </c>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
       <c r="N76" s="4" t="n"/>
-      <c r="O76" s="4" t="n"/>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>One Drive</t>
+        </is>
+      </c>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
-      <c r="R76" s="4" t="n"/>
-      <c r="S76" s="5" t="n"/>
-      <c r="T76" s="4" t="n"/>
+      <c r="R76" s="4" t="inlineStr">
+        <is>
+          <t>Human footprint areas &gt;4 in the Ucayali department for 2012, 2015, 2018, and 2021, derived from Peru´s Human Footprint map. The original raster data was converted to vector polygons and aggregated by adminstrative provinces and districts level</t>
+        </is>
+      </c>
+      <c r="S76" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T76" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U76" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V76" s="21" t="inlineStr">
+        <is>
+          <t>https://geoservidor.minam.gob.pe/recursos/intercambio-de-datos/</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="21.75" customHeight="1">
-      <c r="A77" s="3" t="n"/>
-      <c r="B77" s="4" t="n"/>
-      <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="n"/>
-      <c r="F77" s="4" t="n"/>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-078</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Physical Vulnerability map</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Pressures / drivers</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
       <c r="G77" s="4" t="n"/>
-      <c r="H77" s="4" t="n"/>
-      <c r="I77" s="4" t="n"/>
-      <c r="J77" s="4" t="n"/>
-      <c r="K77" s="4" t="n"/>
-      <c r="L77" s="4" t="n"/>
-      <c r="M77" s="4" t="n"/>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>Other (specify in notes)</t>
+        </is>
+      </c>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
       <c r="N77" s="4" t="n"/>
-      <c r="O77" s="4" t="n"/>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>One Drive</t>
+        </is>
+      </c>
       <c r="P77" s="4" t="n"/>
       <c r="Q77" s="4" t="n"/>
-      <c r="R77" s="4" t="n"/>
-      <c r="S77" s="5" t="n"/>
-      <c r="T77" s="4" t="n"/>
+      <c r="R77" s="4" t="inlineStr">
+        <is>
+          <t>Spatial distribution of physical vulnerability levels within the Ucayali department, derived from Peru’s National Physical Vulnerability map 2011, and aggregated by administrative provinces and districts level</t>
+        </is>
+      </c>
+      <c r="S77" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T77" s="4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="U77" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V77" s="10" t="inlineStr">
+        <is>
+          <t>https://geoservidor.minam.gob.pe/recursos/intercambio-de-datos/</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="21.75" customHeight="1">
-      <c r="A78" s="3" t="n"/>
-      <c r="B78" s="4" t="n"/>
-      <c r="C78" s="4" t="n"/>
-      <c r="D78" s="4" t="n"/>
-      <c r="E78" s="4" t="n"/>
-      <c r="F78" s="4" t="n"/>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-079</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Forest/Non-forest 2000/Forest loss 2001-2024</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Pressures / drivers</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
       <c r="G78" s="4" t="n"/>
-      <c r="H78" s="4" t="n"/>
-      <c r="I78" s="4" t="n"/>
-      <c r="J78" s="4" t="n"/>
-      <c r="K78" s="4" t="n"/>
-      <c r="L78" s="4" t="n"/>
-      <c r="M78" s="4" t="n"/>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>2000-2024</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>Other (specify in notes)</t>
+        </is>
+      </c>
+      <c r="M78" s="4" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
       <c r="N78" s="4" t="n"/>
-      <c r="O78" s="4" t="n"/>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>One Drive</t>
+        </is>
+      </c>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
-      <c r="R78" s="4" t="n"/>
-      <c r="S78" s="5" t="n"/>
-      <c r="T78" s="4" t="n"/>
+      <c r="R78" s="4" t="inlineStr">
+        <is>
+          <t>Forest/non-forest baseline for 2000 and annual forest loss from 2001 to 2024 in Ucayali, derived from MINAM’s GEOBOSQUES forest monitoring dataset and spatially aggregated by provinces and districts.</t>
+        </is>
+      </c>
+      <c r="S78" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T78" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U78" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V78" s="21" t="inlineStr">
+        <is>
+          <t>https://geobosques.minam.gob.pe/geobosque/view/descargas.php?122345gxxe345w34gg#download</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="21.75" customHeight="1">
-      <c r="A79" s="3" t="n"/>
-      <c r="B79" s="4" t="n"/>
-      <c r="C79" s="4" t="n"/>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="n"/>
-      <c r="F79" s="4" t="n"/>
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-080</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Annual deforestation</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Pressures / drivers</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
       <c r="G79" s="4" t="n"/>
-      <c r="H79" s="4" t="n"/>
-      <c r="I79" s="4" t="n"/>
-      <c r="J79" s="4" t="n"/>
-      <c r="K79" s="4" t="n"/>
-      <c r="L79" s="4" t="n"/>
-      <c r="M79" s="4" t="n"/>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>2001-2024</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>Other (specify in notes)</t>
+        </is>
+      </c>
+      <c r="M79" s="4" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
       <c r="N79" s="4" t="n"/>
-      <c r="O79" s="4" t="n"/>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>One Drive</t>
+        </is>
+      </c>
       <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
-      <c r="R79" s="4" t="n"/>
-      <c r="S79" s="5" t="n"/>
-      <c r="T79" s="4" t="n"/>
+      <c r="R79" s="4" t="inlineStr">
+        <is>
+          <t>Annual forest loss from 2001-2025 in Ucayali, derived from MINAM’s GEOBOSQUES forest monitoring dataset and spatially aggregated by provinces and districts</t>
+        </is>
+      </c>
+      <c r="S79" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T79" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U79" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V79" s="10" t="inlineStr">
+        <is>
+          <t>https://geobosques.minam.gob.pe/geobosque/view/descargas.php?122345gxxe345w34gg#download</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="21.75" customHeight="1">
-      <c r="A80" s="3" t="n"/>
-      <c r="B80" s="4" t="n"/>
-      <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="n"/>
-      <c r="F80" s="4" t="n"/>
-      <c r="G80" s="4" t="n"/>
-      <c r="H80" s="4" t="n"/>
-      <c r="I80" s="4" t="n"/>
-      <c r="J80" s="4" t="n"/>
-      <c r="K80" s="4" t="n"/>
-      <c r="L80" s="4" t="n"/>
-      <c r="M80" s="4" t="n"/>
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-081</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Land Cover and Land Use</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Land cover / land use</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>30 m (original dataset)</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>2000, 2005, 2010, 2015, 2020, 2024</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>Other (specify in notes)</t>
+        </is>
+      </c>
+      <c r="M80" s="4" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
       <c r="N80" s="4" t="n"/>
-      <c r="O80" s="4" t="n"/>
+      <c r="O80" s="4" t="inlineStr">
+        <is>
+          <t>One Drive</t>
+        </is>
+      </c>
       <c r="P80" s="4" t="n"/>
       <c r="Q80" s="4" t="n"/>
-      <c r="R80" s="4" t="n"/>
-      <c r="S80" s="5" t="n"/>
-      <c r="T80" s="4" t="n"/>
+      <c r="R80" s="4" t="inlineStr">
+        <is>
+          <t>Land cover and land-use classification within the Ucayali department for 2000, 2005, 2010, 2015, 2020 and 2024, derived from Mapbiomas Peru Collection 4. The original raster data was converted to vector polygons and aggregated by administrative provinces and districts level</t>
+        </is>
+      </c>
+      <c r="S80" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T80" s="4" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U80" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V80" s="21" t="inlineStr">
+        <is>
+          <t>https://peru.mapbiomas.org/iniciativas-y-productos/cobertura-y-uso-del-suelo/cobertura/</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="21.75" customHeight="1">
-      <c r="A81" s="3" t="n"/>
-      <c r="B81" s="4" t="n"/>
-      <c r="C81" s="4" t="n"/>
-      <c r="D81" s="4" t="n"/>
-      <c r="E81" s="4" t="n"/>
-      <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
-      <c r="J81" s="4" t="n"/>
-      <c r="K81" s="4" t="n"/>
-      <c r="L81" s="4" t="n"/>
-      <c r="M81" s="4" t="n"/>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>MFL-2026-082</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Annual Burned Area</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Pressures / drivers</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>PER-PCL — Pucallpa – Ucayali</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>30 m (original dataset)</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>2013-2024</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>Alliance Bioversity-CIAT</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>Beatriz Rodríguez (b.rodriguez@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>Other (specify in notes)</t>
+        </is>
+      </c>
+      <c r="M81" s="4" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
       <c r="N81" s="4" t="n"/>
-      <c r="O81" s="4" t="n"/>
+      <c r="O81" s="4" t="inlineStr">
+        <is>
+          <t>One Drive</t>
+        </is>
+      </c>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
-      <c r="R81" s="4" t="n"/>
-      <c r="S81" s="5" t="n"/>
-      <c r="T81" s="4" t="n"/>
+      <c r="R81" s="4" t="inlineStr">
+        <is>
+          <t>Cumulative Burned Area during 2013–2024 within the Ucayali department, derived from Mapbiomas Peru Collection 1. The original raster data was converted to vector polygons and aggregated by administrative provinces and districts level</t>
+        </is>
+      </c>
+      <c r="S81" s="5" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="T81" s="4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U81" s="11" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V81" s="10" t="inlineStr">
+        <is>
+          <t>https://peru.mapbiomas.org/iniciativas-y-productos/fuego/mapeo-anual/</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="21.75" customHeight="1">
       <c r="A82" s="3" t="n"/>
@@ -9344,175 +10557,136 @@
       <c r="T103" s="4" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>MFL-2026-068</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>Tree conservation and restoration priority areas</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr">
-        <is>
-          <t>Laos</t>
-        </is>
-      </c>
-      <c r="D104" s="4" t="inlineStr">
-        <is>
-          <t>Decision-support outputs</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>NATIONAL — Country-wide coverage</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>Raster</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>1000m</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>2017-2025</t>
-        </is>
-      </c>
-      <c r="I104" s="4" t="inlineStr">
-        <is>
-          <t>Alliance Bioversity-CIAT</t>
-        </is>
-      </c>
-      <c r="J104" s="23" t="inlineStr">
-        <is>
-          <t>Hannes Gaisberger, h.gaisberger@cgiar.org</t>
-        </is>
-      </c>
-      <c r="K104" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>CGIAR Open Access</t>
-        </is>
-      </c>
-      <c r="O104" s="4" t="inlineStr">
-        <is>
-          <t>One drive</t>
-        </is>
-      </c>
-      <c r="R104" s="4" t="inlineStr">
-        <is>
-          <t>Conservation for Restoration (C4R) tool LAOS: mapping the vulnerability and priority areas for conservation and restoration of 79 native tree species. Linked to D4R</t>
-        </is>
-      </c>
-      <c r="T104" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="U104" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On-demand </t>
-        </is>
-      </c>
-      <c r="W104" s="20" t="inlineStr">
-        <is>
-          <t>250 MB</t>
-        </is>
-      </c>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="n"/>
+      <c r="H104" s="4" t="n"/>
+      <c r="I104" s="4" t="n"/>
+      <c r="J104" s="23" t="n"/>
+      <c r="K104" s="4" t="n"/>
+      <c r="L104" s="4" t="n"/>
+      <c r="O104" s="4" t="n"/>
+      <c r="R104" s="4" t="n"/>
+      <c r="T104" s="4" t="n"/>
+      <c r="U104" s="8" t="n"/>
+      <c r="W104" s="20" t="n"/>
     </row>
     <row r="105" ht="30" customHeight="1">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>MFL-2026-069</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="inlineStr">
-        <is>
-          <t>Tree conservation and restoration priority areas</t>
-        </is>
-      </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>Vietnam</t>
-        </is>
-      </c>
-      <c r="D105" s="4" t="inlineStr">
-        <is>
-          <t>Decision-support outputs</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>NATIONAL — Country-wide coverage</t>
-        </is>
-      </c>
-      <c r="F105" s="4" t="inlineStr">
-        <is>
-          <t>Raster</t>
-        </is>
-      </c>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>1000m</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>2017-2025</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="inlineStr">
-        <is>
-          <t>Alliance Bioversity-CIAT</t>
-        </is>
-      </c>
-      <c r="J105" s="23" t="inlineStr">
-        <is>
-          <t>Hannes Gaisberger, h.gaisberger@cgiar.org</t>
-        </is>
-      </c>
-      <c r="K105" s="4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L105" s="4" t="inlineStr">
-        <is>
-          <t>CGIAR Open Access</t>
-        </is>
-      </c>
-      <c r="O105" s="4" t="inlineStr">
-        <is>
-          <t>One drive</t>
-        </is>
-      </c>
-      <c r="R105" s="4" t="inlineStr">
-        <is>
-          <t>Conservation for Restoration (C4R) tool VIETNAM: mapping the vulnerability and priority areas for conservation and restoration of 66 native tree species. Linked to D4R</t>
-        </is>
-      </c>
-      <c r="T105" s="4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="U105" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On-demand </t>
-        </is>
-      </c>
-      <c r="W105" s="20" t="inlineStr">
-        <is>
-          <t>250 MB</t>
-        </is>
-      </c>
-    </row>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="n"/>
+      <c r="E105" s="4" t="n"/>
+      <c r="F105" s="4" t="n"/>
+      <c r="G105" s="4" t="n"/>
+      <c r="H105" s="4" t="n"/>
+      <c r="I105" s="4" t="n"/>
+      <c r="J105" s="23" t="n"/>
+      <c r="K105" s="4" t="n"/>
+      <c r="L105" s="4" t="n"/>
+      <c r="O105" s="4" t="n"/>
+      <c r="R105" s="4" t="n"/>
+      <c r="T105" s="4" t="n"/>
+      <c r="U105" s="8" t="n"/>
+      <c r="W105" s="20" t="n"/>
+    </row>
+    <row r="106"/>
+    <row r="107"/>
+    <row r="108"/>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114"/>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131"/>
+    <row r="132"/>
+    <row r="133"/>
+    <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
   </sheetData>
   <autoFilter ref="A2:W105"/>
   <conditionalFormatting sqref="K3:K105">
@@ -9536,80 +10710,32 @@
       <formula>P3="Registered only"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="7">
-    <dataValidation sqref="U3:U104" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
-      <formula1>INDIRECT("Table11[Update frequency]")</formula1>
+  <dataValidations count="8">
+    <dataValidation sqref="C3:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=MOSAIC_Countries</formula1>
     </dataValidation>
-    <dataValidation sqref="C3:C200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the Countries list (Reference sheet)." type="list" errorStyle="warning">
-      <formula1>='Reference'!$A$2:$A$16</formula1>
+    <dataValidation sqref="D3:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=MOSAIC_Themes</formula1>
     </dataValidation>
-    <dataValidation sqref="D3:D200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the MFL Themes list (Reference sheet)." type="list" errorStyle="warning">
-      <formula1>='Reference'!$C$2:$C$15</formula1>
+    <dataValidation sqref="E3:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=MOSAIC_LLs</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the Living Landscapes list (Reference sheet)." type="list" errorStyle="warning">
-      <formula1>='Reference'!$K$2:$K$14</formula1>
+    <dataValidation sqref="F3:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=MOSAIC_DataTypes</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the Data types list (Reference sheet)." type="list" errorStyle="warning">
-      <formula1>='Reference'!$E$2:$E$7</formula1>
+    <dataValidation sqref="I3:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=MOSAIC_Sources</formula1>
     </dataValidation>
-    <dataValidation sqref="I3:I200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the Centres / Sources list (Reference sheet)." type="list" errorStyle="warning">
-      <formula1>='Reference'!$G$2:$G$18</formula1>
+    <dataValidation sqref="K3:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=MOSAIC_Access</formula1>
     </dataValidation>
-    <dataValidation sqref="K3:K200" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Pick a value from the Access levels list (Reference sheet)." type="list" errorStyle="warning">
-      <formula1>='Reference'!$I$2:$I$4</formula1>
+    <dataValidation sqref="P3:P200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=MOSAIC_Migration</formula1>
+    </dataValidation>
+    <dataValidation sqref="U3:U200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=MOSAIC_UpdFreq</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V4" display="https://drive.google.com/file/d/1CPV03S47s0asEJqdAozbNOT1lkgr0YkG/view?usp=sharing" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V11" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V15" display="https://zenodo.org/records/10846594" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V16" display="https://github.com/core-stack-org/QGIS-Styles/blob/main/Tree%20Health/ccd_style.qml" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V18" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V20" location="mapCenter=-14.06266%2C13.65709%2C11.00&amp;mode=step&amp;timeExtent=2017%2C2022&amp;year=2023" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" display="dieyemohamadou@gmail.com " r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V21" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" display="dieyemohamadou@gmail.com " r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V22" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" display="dieyemohamadou@gmail.com " r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" display="dieyemohamadou@gmail.com " r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V24" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" display="dieyemohamadou@gmail.com " r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" display="dieyemohamadou@gmail.com " r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" display="dieyemohamadou@gmail.com " r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V27" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" display="h.gaisberger@cgiar.org" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V28" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V31" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V35" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V36" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V37" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" display="s.douangsavanh@cgiar.org" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" display="s.douangsavanh@cgiar.org" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V60" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V61" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V62" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V63" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V64" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V65" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V66" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V67" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V68" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" display="h.gaisberger@cgiar.org" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" display="h.gaisberger@cgiar.org" r:id="rId49"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -10712,28 +10712,28 @@
   </conditionalFormatting>
   <dataValidations count="8">
     <dataValidation sqref="C3:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=MOSAIC_Countries</formula1>
+      <formula1>MOSAIC_Countries</formula1>
     </dataValidation>
     <dataValidation sqref="D3:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=MOSAIC_Themes</formula1>
+      <formula1>MOSAIC_Themes</formula1>
     </dataValidation>
     <dataValidation sqref="E3:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=MOSAIC_LLs</formula1>
+      <formula1>MOSAIC_LLs</formula1>
     </dataValidation>
     <dataValidation sqref="F3:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=MOSAIC_DataTypes</formula1>
+      <formula1>MOSAIC_DataTypes</formula1>
     </dataValidation>
     <dataValidation sqref="I3:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=MOSAIC_Sources</formula1>
+      <formula1>MOSAIC_Sources</formula1>
     </dataValidation>
     <dataValidation sqref="K3:K200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=MOSAIC_Access</formula1>
+      <formula1>MOSAIC_Access</formula1>
     </dataValidation>
     <dataValidation sqref="P3:P200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=MOSAIC_Migration</formula1>
+      <formula1>MOSAIC_Migration</formula1>
     </dataValidation>
     <dataValidation sqref="U3:U200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=MOSAIC_UpdFreq</formula1>
+      <formula1>MOSAIC_UpdFreq</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -20,7 +20,7 @@
     <definedName name="MOSAIC_Access">Reference!$I$2:$I$4</definedName>
     <definedName name="MOSAIC_Migration">Reference!$O$2:$O$3</definedName>
     <definedName name="MOSAIC_UpdFreq">Reference!$Q$2:$Q$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1221,7 +1221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W81"/>
+  <dimension ref="A1:W82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8977,8 +8977,105 @@
       </c>
       <c r="W81" s="8" t="n"/>
     </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-083</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Crop type map</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Ecosystem condition</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>Raster</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>10m</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
+        <is>
+          <t>IFPRI</t>
+        </is>
+      </c>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>z.guo@cgiar.org</t>
+        </is>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>CGIAR Open Access</t>
+        </is>
+      </c>
+      <c r="M82" s="10" t="inlineStr">
+        <is>
+          <t>Validated</t>
+        </is>
+      </c>
+      <c r="N82" s="10" t="n"/>
+      <c r="O82" s="10" t="inlineStr">
+        <is>
+          <t>One drive</t>
+        </is>
+      </c>
+      <c r="P82" s="10" t="n"/>
+      <c r="Q82" s="10" t="n"/>
+      <c r="R82" s="11" t="inlineStr">
+        <is>
+          <t>Major crop type maps in Nandi county, Kenya</t>
+        </is>
+      </c>
+      <c r="S82" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="T82" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="U82" s="10" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V82" s="10" t="n"/>
+      <c r="W82" s="10" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:W81"/>
+  <autoFilter ref="A2:W82"/>
   <conditionalFormatting sqref="K3:K300">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Open"</formula>

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -7944,7 +7944,7 @@
       </c>
       <c r="L71" s="8" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
         </is>
       </c>
       <c r="M71" s="8" t="inlineStr">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="L72" s="10" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
         </is>
       </c>
       <c r="M72" s="10" t="inlineStr">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
         </is>
       </c>
       <c r="M73" s="8" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Free download from RAISG; no formal license stated</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="L75" s="8" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
         </is>
       </c>
       <c r="M75" s="8" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
         </is>
       </c>
       <c r="M76" s="10" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="L77" s="8" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
         </is>
       </c>
       <c r="M77" s="8" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="L78" s="10" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="L79" s="8" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>Free download from the Peruvian government source (MINAM/GEOBOSQUES, SERNANP, INEI); no formal license stated</t>
         </is>
       </c>
       <c r="M79" s="8" t="inlineStr">
@@ -8750,7 +8750,7 @@
       <c r="Q79" s="8" t="n"/>
       <c r="R79" s="9" t="inlineStr">
         <is>
-          <t>Annual forest loss from 2001-2025 in Ucayali, derived from MINAM’s GEOBOSQUES forest monitoring dataset and spatially aggregated by provinces and districts</t>
+          <t>Annual forest loss from 2001-2024 in Ucayali, derived from MINAM’s GEOBOSQUES forest monitoring dataset and spatially aggregated by provinces and districts. The 2025 update published at source is not yet included in this layer.</t>
         </is>
       </c>
       <c r="S79" s="8" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>Annual Burned Area</t>
+          <t>Accumulated Burned Area 2013-2024</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="L81" s="8" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>CC BY 4.0</t>
         </is>
       </c>
       <c r="M81" s="8" t="inlineStr">

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -20,7 +20,7 @@
     <definedName name="MOSAIC_Access">Reference!$I$2:$I$4</definedName>
     <definedName name="MOSAIC_Migration">Reference!$O$2:$O$3</definedName>
     <definedName name="MOSAIC_UpdFreq">Reference!$Q$2:$Q$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1221,7 +1221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W82"/>
+  <dimension ref="A1:W83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5409,17 +5409,17 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>admin-level-1, admin-level-2, admin-level-3</t>
+          <t>admin-level-0 to admin-level-4 (GADM 4.1)</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>National government (external)</t>
+          <t>AfricaRice</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
@@ -5452,11 +5452,15 @@
       <c r="Q45" s="8" t="n"/>
       <c r="R45" s="9" t="inlineStr">
         <is>
-          <t>Administrative boundaries</t>
+          <t>GADM 4.1 administrative boundaries for Côte d'Ivoire, levels 0 to 4: the country; 12 districts and 2 autonomous districts; 31 regions plus the 2 autonomous districts; 113 departments; and 191 sub-prefectures. Country-wide, not clipped to the N'Zi landscape. Unmodified from GADM; download from gadm.org. GADM's licence does not allow redistribution, so MOSAIC keeps only an internal quality-control copy.</t>
         </is>
       </c>
       <c r="S45" s="8" t="n"/>
-      <c r="T45" s="8" t="n"/>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
       <c r="U45" s="8" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -5464,7 +5468,7 @@
       </c>
       <c r="V45" s="8" t="inlineStr">
         <is>
-          <t>GADM maps and data (gadm.org)</t>
+          <t>https://gadm.org/download_country.html</t>
         </is>
       </c>
       <c r="W45" s="8" t="n"/>
@@ -5596,7 +5600,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>since 2014</t>
+          <t>1980-2010</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
@@ -5616,7 +5620,7 @@
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
-          <t>Other (specify in notes)</t>
+          <t>ARCWeather usage terms: non-commercial, educational, research or personal use only, with citation. The portal states that Côte d'Ivoire climate data is distributed by Sodexam; no licence stated by the rights holder</t>
         </is>
       </c>
       <c r="M47" s="8" t="inlineStr">
@@ -5634,7 +5638,7 @@
       <c r="Q47" s="8" t="n"/>
       <c r="R47" s="9" t="inlineStr">
         <is>
-          <t>Climate data from climate stations for three major cities in the watershed (coverage period varies depending on the station); climate data from M'Be research station</t>
+          <t>Daily weather data for three synoptic stations in and around the N'Zi watershed, served by AfricaRice's ARCWeather portal: Bouaké and Ferkessédougou from 1980 to 2010, Korhogo from 1994 to 2001. Korhogo holds fewer variables, and its dew point is estimated from the minimum temperature. AfricaRice's own M'Bé research-station data from 2014 onward is a separate record, MFL-2026-084.</t>
         </is>
       </c>
       <c r="S47" s="8" t="n"/>
@@ -5645,12 +5649,12 @@
       </c>
       <c r="U47" s="8" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Static</t>
         </is>
       </c>
       <c r="V47" s="8" t="inlineStr">
         <is>
-          <t>NHMS for the synoptic climate stations</t>
+          <t>https://arcweather.africarice.org/en/downloads</t>
         </is>
       </c>
       <c r="W47" s="8" t="n"/>
@@ -5663,12 +5667,12 @@
       </c>
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>DSSAT soil profiles (global .SOL files)</t>
+          <t>DSSAT soil profiles for Côte d'Ivoire (CI.SOL)</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
@@ -5678,10 +5682,14 @@
       </c>
       <c r="E48" s="10" t="inlineStr">
         <is>
-          <t>GLOBAL — Global / cross-landscape</t>
-        </is>
-      </c>
-      <c r="F48" s="10" t="n"/>
+          <t>NATIONAL — Country-wide coverage</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>Tabular</t>
+        </is>
+      </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
           <t>5-min resolution</t>
@@ -5717,7 +5725,11 @@
           <t>Validated</t>
         </is>
       </c>
-      <c r="N48" s="10" t="n"/>
+      <c r="N48" s="10" t="inlineStr">
+        <is>
+          <t>CI.SOL</t>
+        </is>
+      </c>
       <c r="O48" s="10" t="inlineStr">
         <is>
           <t>server and drive</t>
@@ -5727,7 +5739,7 @@
       <c r="Q48" s="10" t="n"/>
       <c r="R48" s="11" t="inlineStr">
         <is>
-          <t>High-resolution soil profile database for crop modeling applications. Files are '*.SOL' file format (DSSAT soil database) for each country worldwide.</t>
+          <t>DSSAT soil profile file for Côte d'Ivoire (CI.SOL): 3,823 soil profiles on a 5-arc-minute grid covering the whole country, 425 of them inside the N'Zi landscape. It is the unmodified Côte d'Ivoire file of the Global High-Resolution Soil Profile Database for Crop Modeling Applications (IRI, MSU and HarvestChoice/IFPRI, 2015), published on the IFPRI Dataverse.</t>
         </is>
       </c>
       <c r="S48" s="10" t="n"/>
@@ -5743,7 +5755,7 @@
       </c>
       <c r="V48" s="10" t="inlineStr">
         <is>
-          <t>International Research Institute for Climate and Society (IRI); Michigan State University (MSU); HarvestChoice, International Food Policy Research Institute (IFPRI), 2015, "Global High-Resolution Soil Profile Database for Crop Modeling Applications", https://doi.org/10.7910/DVN/1PEEY0</t>
+          <t>https://doi.org/10.7910/DVN/1PEEY0</t>
         </is>
       </c>
       <c r="W48" s="10" t="n"/>
@@ -7320,12 +7332,12 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>SoilGrids gridded soil information</t>
+          <t>iSDAsoil soil properties for the N'Zi watershed (0-20 and 20-50 cm)</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
@@ -7335,13 +7347,17 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>GLOBAL — Global / cross-landscape</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="n"/>
+          <t>CIV-NZ — N'Zi Watershed</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>Raster</t>
+        </is>
+      </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>250 m</t>
+          <t>30 m</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -7384,7 +7400,7 @@
       <c r="Q65" s="8" t="n"/>
       <c r="R65" s="9" t="inlineStr">
         <is>
-          <t>Soil data from SoilGrids</t>
+          <t>Fifteen soil properties from iSDAsoil (iSDA), extracted by AfricaRice for the N'Zi watershed at about 30 m, at 0-20 and 20-50 cm: bulk density, calcium, cation exchange capacity, clay, iron, potassium, magnesium, total nitrogen, phosphorus, pH, sulphur, sand, silt, soil organic carbon and zinc, in physical units. The public source is iSDAsoil for Africa.</t>
         </is>
       </c>
       <c r="S65" s="8" t="n"/>
@@ -7400,7 +7416,7 @@
       </c>
       <c r="V65" s="8" t="inlineStr">
         <is>
-          <t>SoilGrids - Global gridded soil information (https://soilgrids.org/)</t>
+          <t>https://www.isda-africa.com/isdasoil/</t>
         </is>
       </c>
       <c r="W65" s="8" t="n"/>
@@ -9074,8 +9090,101 @@
       <c r="V82" s="10" t="n"/>
       <c r="W82" s="10" t="n"/>
     </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-084</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Climate data AfricaRice M'Bé Research Station</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>Côte d'Ivoire</t>
+        </is>
+      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Water / hydrology</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>CIV-NZ — N'Zi Watershed</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>Tabular</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr">
+        <is>
+          <t>Point level</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>2014 - present</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>AfricaRice</t>
+        </is>
+      </c>
+      <c r="J83" s="8" t="inlineStr">
+        <is>
+          <t>Louis Kouadio (a.kouadio2@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K83" s="8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="L83" s="8" t="inlineStr">
+        <is>
+          <t>AfricaRice Terms of Use (https://www.africarice.org/privacy-policy), the usage policy linked from ARCWeather: attribution with the ARCWeather citation; non-commercial, research, educational or personal use only; reuse under the same conditions. No formal licence issued for the climate data yet</t>
+        </is>
+      </c>
+      <c r="M83" s="8" t="n"/>
+      <c r="N83" s="8" t="n"/>
+      <c r="O83" s="8" t="n"/>
+      <c r="P83" s="8" t="n"/>
+      <c r="Q83" s="8" t="n"/>
+      <c r="R83" s="9" t="inlineStr">
+        <is>
+          <t>Daily weather data from AfricaRice's two weather stations at the M'Bé research station near Bouaké, in the N'Zi watershed: MBE_LOWLAND (273 m) and MBE_UPLAND (303 m), from 2014 onward. Served by AfricaRice's ARCWeather portal.</t>
+        </is>
+      </c>
+      <c r="S83" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="T83" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U83" s="8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="V83" s="8" t="inlineStr">
+        <is>
+          <t>https://arcweather.africarice.org/en/downloads</t>
+        </is>
+      </c>
+      <c r="W83" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:W82"/>
+  <autoFilter ref="A2:W83"/>
   <conditionalFormatting sqref="K3:K300">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Open"</formula>

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -5180,11 +5180,7 @@
           <t>Agroecological zonations</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
+      <c r="S42" s="10" t="n"/>
       <c r="T42" s="10" t="n"/>
       <c r="U42" s="10" t="n"/>
       <c r="V42" s="10" t="inlineStr">
@@ -5269,11 +5265,7 @@
           <t>Agroecological zonations</t>
         </is>
       </c>
-      <c r="S43" s="8" t="inlineStr">
-        <is>
-          <t>Drive</t>
-        </is>
-      </c>
+      <c r="S43" s="8" t="n"/>
       <c r="T43" s="8" t="n"/>
       <c r="U43" s="8" t="inlineStr">
         <is>
@@ -5839,11 +5831,7 @@
           <t>MRC produced the data</t>
         </is>
       </c>
-      <c r="S49" s="8" t="inlineStr">
-        <is>
-          <t>MRC produced the data</t>
-        </is>
-      </c>
+      <c r="S49" s="8" t="n"/>
       <c r="T49" s="8" t="inlineStr">
         <is>
           <t>NA</t>
@@ -5940,11 +5928,7 @@
           <t>MRC produced the data</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>MRC produced the data</t>
-        </is>
-      </c>
+      <c r="S50" s="10" t="n"/>
       <c r="T50" s="10" t="inlineStr">
         <is>
           <t>NA</t>

--- a/catalog/MFL_Dataset_Registry.xlsx
+++ b/catalog/MFL_Dataset_Registry.xlsx
@@ -20,7 +20,7 @@
     <definedName name="MOSAIC_Access">Reference!$I$2:$I$4</definedName>
     <definedName name="MOSAIC_Migration">Reference!$O$2:$O$3</definedName>
     <definedName name="MOSAIC_UpdFreq">Reference!$Q$2:$Q$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">' Registry'!$A$2:$W$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1221,7 +1221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W83"/>
+  <dimension ref="A1:W91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9167,8 +9167,816 @@
       </c>
       <c r="W83" s="8" t="n"/>
     </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-085</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Landscape Resources</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>Ecosystem services</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>Basin level</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>ILRI</t>
+        </is>
+      </c>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>Ambica Paliwal (a.paliwal@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K84" s="10" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>Restricted — contact data owner</t>
+        </is>
+      </c>
+      <c r="M84" s="10" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="N84" s="10" t="n"/>
+      <c r="O84" s="10" t="inlineStr">
+        <is>
+          <t>One drive</t>
+        </is>
+      </c>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="10" t="n"/>
+      <c r="R84" s="11" t="inlineStr">
+        <is>
+          <t>Key natural resources and the ecosystem services they provide to local communities.</t>
+        </is>
+      </c>
+      <c r="S84" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T84" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U84" s="10" t="inlineStr">
+        <is>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V84" s="10" t="inlineStr">
+        <is>
+          <t>Internal Available on Request</t>
+        </is>
+      </c>
+      <c r="W84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-086</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Resource change</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Ecosystem condition</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>Basin level</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>ILRI</t>
+        </is>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>Ambica Paliwal (a.paliwal@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K85" s="8" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>Restricted — contact data owner</t>
+        </is>
+      </c>
+      <c r="M85" s="8" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="N85" s="8" t="n"/>
+      <c r="O85" s="8" t="inlineStr">
+        <is>
+          <t>One drive</t>
+        </is>
+      </c>
+      <c r="P85" s="8" t="n"/>
+      <c r="Q85" s="8" t="n"/>
+      <c r="R85" s="9" t="inlineStr">
+        <is>
+          <t>Changes in the condition and availability of key resources over time.</t>
+        </is>
+      </c>
+      <c r="S85" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T85" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U85" s="8" t="inlineStr">
+        <is>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V85" s="8" t="inlineStr">
+        <is>
+          <t>Internal Available on Request</t>
+        </is>
+      </c>
+      <c r="W85" s="8" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-087</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Environmental challenges</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Degradation / land health</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>Basin level</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>ILRI</t>
+        </is>
+      </c>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>Ambica Paliwal (a.paliwal@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K86" s="10" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>Restricted — contact data owner</t>
+        </is>
+      </c>
+      <c r="M86" s="10" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="N86" s="10" t="n"/>
+      <c r="O86" s="10" t="inlineStr">
+        <is>
+          <t>One drive</t>
+        </is>
+      </c>
+      <c r="P86" s="10" t="n"/>
+      <c r="Q86" s="10" t="n"/>
+      <c r="R86" s="11" t="inlineStr">
+        <is>
+          <t>Areas affected by environmental degradation and land-health challenges.</t>
+        </is>
+      </c>
+      <c r="S86" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T86" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U86" s="10" t="inlineStr">
+        <is>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V86" s="10" t="inlineStr">
+        <is>
+          <t>Internal Available on Request</t>
+        </is>
+      </c>
+      <c r="W86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-088</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>Climate risks</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D87" s="8" t="inlineStr">
+        <is>
+          <t>Ecosystem condition</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+        </is>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr">
+        <is>
+          <t>Basin level</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>ILRI</t>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>Ambica Paliwal (a.paliwal@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="L87" s="8" t="inlineStr">
+        <is>
+          <t>Restricted — contact data owner</t>
+        </is>
+      </c>
+      <c r="M87" s="8" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="N87" s="8" t="n"/>
+      <c r="O87" s="8" t="inlineStr">
+        <is>
+          <t>One drive</t>
+        </is>
+      </c>
+      <c r="P87" s="8" t="n"/>
+      <c r="Q87" s="8" t="n"/>
+      <c r="R87" s="9" t="inlineStr">
+        <is>
+          <t>Areas exposed to climate-related environmental risks and stress.</t>
+        </is>
+      </c>
+      <c r="S87" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T87" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U87" s="8" t="inlineStr">
+        <is>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V87" s="8" t="inlineStr">
+        <is>
+          <t>Internal Available on Request</t>
+        </is>
+      </c>
+      <c r="W87" s="8" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-089</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>Livelihood resources</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Socio-economic / livelihoods</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>Basin level</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>ILRI</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>Ambica Paliwal (a.paliwal@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>Restricted — contact data owner</t>
+        </is>
+      </c>
+      <c r="M88" s="10" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="N88" s="10" t="n"/>
+      <c r="O88" s="10" t="inlineStr">
+        <is>
+          <t>One drive</t>
+        </is>
+      </c>
+      <c r="P88" s="10" t="n"/>
+      <c r="Q88" s="10" t="n"/>
+      <c r="R88" s="11" t="inlineStr">
+        <is>
+          <t>Resources and infrastructure that support local livelihoods and economic activities.</t>
+        </is>
+      </c>
+      <c r="S88" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T88" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U88" s="10" t="inlineStr">
+        <is>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V88" s="10" t="inlineStr">
+        <is>
+          <t>Internal Available on Request</t>
+        </is>
+      </c>
+      <c r="W88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-090</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>Conflicts</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Socio-economic / livelihoods</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr">
+        <is>
+          <t>Basin level</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>ILRI</t>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>Ambica Paliwal (a.paliwal@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K89" s="8" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="L89" s="8" t="inlineStr">
+        <is>
+          <t>Restricted — contact data owner</t>
+        </is>
+      </c>
+      <c r="M89" s="8" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="N89" s="8" t="n"/>
+      <c r="O89" s="8" t="inlineStr">
+        <is>
+          <t>One drive</t>
+        </is>
+      </c>
+      <c r="P89" s="8" t="n"/>
+      <c r="Q89" s="8" t="n"/>
+      <c r="R89" s="9" t="inlineStr">
+        <is>
+          <t>Locations and resources affected by conflicts and competing uses</t>
+        </is>
+      </c>
+      <c r="S89" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T89" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U89" s="8" t="inlineStr">
+        <is>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V89" s="8" t="inlineStr">
+        <is>
+          <t>Internal Available on Request</t>
+        </is>
+      </c>
+      <c r="W89" s="8" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>MFL-2026-091</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>Drivers of change</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Pressures / drivers</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>Basin level</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>ILRI</t>
+        </is>
+      </c>
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>Ambica Paliwal (a.paliwal@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K90" s="10" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>Restricted — contact data owner</t>
+        </is>
+      </c>
+      <c r="M90" s="10" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="N90" s="10" t="n"/>
+      <c r="O90" s="10" t="inlineStr">
+        <is>
+          <t>One drive</t>
+        </is>
+      </c>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="10" t="n"/>
+      <c r="R90" s="11" t="inlineStr">
+        <is>
+          <t>Key human and environmental drivers influencing landscape change.</t>
+        </is>
+      </c>
+      <c r="S90" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T90" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U90" s="10" t="inlineStr">
+        <is>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V90" s="10" t="inlineStr">
+        <is>
+          <t>Internal Available on Request</t>
+        </is>
+      </c>
+      <c r="W90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>MFL-2026-092</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Restoration opportunities</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Decision-support outputs</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>KEN-LVB — Lake Victoria Basin (Kenya)</t>
+        </is>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>Vector</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr">
+        <is>
+          <t>Basin level</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>ILRI</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t>Ambica Paliwal (a.paliwal@cgiar.org)</t>
+        </is>
+      </c>
+      <c r="K91" s="8" t="inlineStr">
+        <is>
+          <t>Restricted</t>
+        </is>
+      </c>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>Restricted — contact data owner</t>
+        </is>
+      </c>
+      <c r="M91" s="8" t="inlineStr">
+        <is>
+          <t>Raw</t>
+        </is>
+      </c>
+      <c r="N91" s="8" t="n"/>
+      <c r="O91" s="8" t="inlineStr">
+        <is>
+          <t>One drive</t>
+        </is>
+      </c>
+      <c r="P91" s="8" t="n"/>
+      <c r="Q91" s="8" t="n"/>
+      <c r="R91" s="9" t="inlineStr">
+        <is>
+          <t>Priority areas and opportunities for restoration and targeted investment.</t>
+        </is>
+      </c>
+      <c r="S91" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T91" s="8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="U91" s="8" t="inlineStr">
+        <is>
+          <t>On-demand</t>
+        </is>
+      </c>
+      <c r="V91" s="8" t="inlineStr">
+        <is>
+          <t>Internal Available on Request</t>
+        </is>
+      </c>
+      <c r="W91" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:W83"/>
+  <autoFilter ref="A2:W91"/>
   <conditionalFormatting sqref="K3:K300">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Open"</formula>
